--- a/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>PKG</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1937900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1936000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1952100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1976300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1978400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2125900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2237300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2136400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2043200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2000100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1879900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1807200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1714200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1693700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1541600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1708700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1720000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1750700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1759900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1733700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1746500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1809900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1767500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1690600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1684300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1640100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1584000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1536500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1476600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1484000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1527800</v>
+      </c>
+      <c r="E9" s="3">
         <v>1523300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1507400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1544900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1528100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1607500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1648500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1603200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1533300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1489400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1431100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1403500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1380900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1348300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1209700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1342900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1336700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1339300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1332000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1312300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1321100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1366700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1346900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1334500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1312600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1242800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1219400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1198000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1149500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1154500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>410100</v>
+      </c>
+      <c r="E10" s="3">
         <v>412700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>444700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>431400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>450300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>518400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>588800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>533200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>509900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>510700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>448800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>403700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>333300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>345400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>331900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>365800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>383300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>411400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>427900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>421400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>425400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>443200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>420600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>356100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>371700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>397300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>364600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>338500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>327100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>329500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,100 +1298,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>58000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-3100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>74600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>7200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>21500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>3500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>6000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1676400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1677400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1667700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1705600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1690400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1765600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1821500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1779900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1745900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1647800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1585300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1568900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1525000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1484200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1425500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1499600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1484900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1487900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1479500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1458300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1459800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1511400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1497900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1477700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1432300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1397800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1350200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1333400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1283700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1277600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>261500</v>
+      </c>
+      <c r="E18" s="3">
         <v>258600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>284400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>270700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>288000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>360300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>415800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>356500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>297300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>352300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>294600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>238300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>189200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>209500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>116100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>209100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>235100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>262800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>280400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>275400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>286700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>298500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>269600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>212900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>252000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>242300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>233800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>203100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>192900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>206400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,22 +1747,23 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-2000</v>
       </c>
       <c r="F20" s="3">
         <v>-2000</v>
       </c>
       <c r="G20" s="3">
-        <v>3600</v>
+        <v>-2000</v>
       </c>
       <c r="H20" s="3">
         <v>3600</v>
@@ -1742,19 +1775,19 @@
         <v>3600</v>
       </c>
       <c r="K20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L20" s="3">
         <v>4900</v>
-      </c>
-      <c r="L20" s="3">
-        <v>5000</v>
       </c>
       <c r="M20" s="3">
         <v>5000</v>
       </c>
       <c r="N20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O20" s="3">
         <v>4800</v>
-      </c>
-      <c r="O20" s="3">
-        <v>600</v>
       </c>
       <c r="P20" s="3">
         <v>600</v>
@@ -1766,19 +1799,19 @@
         <v>600</v>
       </c>
       <c r="S20" s="3">
+        <v>600</v>
+      </c>
+      <c r="T20" s="3">
         <v>-3100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3200</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-3300</v>
       </c>
       <c r="V20" s="3">
         <v>-3300</v>
       </c>
       <c r="W20" s="3">
-        <v>-1300</v>
+        <v>-3300</v>
       </c>
       <c r="X20" s="3">
         <v>-1300</v>
@@ -1787,11 +1820,11 @@
         <v>-1300</v>
       </c>
       <c r="Z20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-700</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1805,378 +1838,393 @@
         <v>0</v>
       </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-23400</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>390500</v>
+      </c>
+      <c r="E21" s="3">
         <v>386200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>410300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>398200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>410400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>477900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>533700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>469800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>408600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>462900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>404300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>343900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>290700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>310600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>224900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>310000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>330900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>357500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>373000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>366900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>382700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>398600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>372400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>320300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>359700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>339800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>327500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>295600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>286600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E22" s="3">
         <v>12300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>23500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>24400</v>
       </c>
       <c r="P22" s="3">
         <v>24400</v>
       </c>
       <c r="Q22" s="3">
+        <v>24400</v>
+      </c>
+      <c r="R22" s="3">
         <v>25100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>59600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>22800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>25600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>28000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>25400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24300</v>
       </c>
-      <c r="AF22" s="3" t="s">
+      <c r="AG22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>248500</v>
+      </c>
+      <c r="E23" s="3">
         <v>244500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>267800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>253300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>276500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>347400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>400600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>340300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>280400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>333900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>274700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>219600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>165400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>185700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>91600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>190100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>172400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>239300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>256000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>249300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>264500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>274100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>245300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>186600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>224000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>216900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>208600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>179100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>168600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E24" s="3">
         <v>61300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>65100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>63200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>64900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>84900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>99100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>86100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>63900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>83200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>67400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>53100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>41800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>46600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>34900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>48400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>36200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>59500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>62400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>62500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>61900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>67400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>58700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>46500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>77200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>77800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>65400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>61700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>57900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>63700</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>189200</v>
+      </c>
+      <c r="E26" s="3">
         <v>183200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>202700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>190100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>211600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>262500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>301500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>254200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>216500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>250700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>207300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>166500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>123600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>139100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>56700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>141700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>136200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>179800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>193600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>186800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>202600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>206700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>186600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>140100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>146800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>139100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>143200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>117400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>110700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>187800</v>
+      </c>
+      <c r="E27" s="3">
         <v>181800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>200800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>188500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>210100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>260600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>298900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>252200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>215000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>249000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>205500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>165200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>122700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>138100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>56200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>140500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>135200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>178500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>192100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>185400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>201000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>205100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>185200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>139000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>144600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>138000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>142000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>116400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>109700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2587,8 +2647,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2605,11 +2665,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>2000</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2617,11 +2677,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>122100</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,22 +2885,25 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E32" s="3">
         <v>1800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>2000</v>
       </c>
       <c r="F32" s="3">
         <v>2000</v>
       </c>
       <c r="G32" s="3">
-        <v>-3600</v>
+        <v>2000</v>
       </c>
       <c r="H32" s="3">
         <v>-3600</v>
@@ -2846,19 +2915,19 @@
         <v>-3600</v>
       </c>
       <c r="K32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="L32" s="3">
         <v>-4900</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-5000</v>
       </c>
       <c r="M32" s="3">
         <v>-5000</v>
       </c>
       <c r="N32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="O32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-600</v>
       </c>
       <c r="P32" s="3">
         <v>-600</v>
@@ -2870,19 +2939,19 @@
         <v>-600</v>
       </c>
       <c r="S32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T32" s="3">
         <v>3100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3200</v>
-      </c>
-      <c r="U32" s="3">
-        <v>3300</v>
       </c>
       <c r="V32" s="3">
         <v>3300</v>
       </c>
       <c r="W32" s="3">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="X32" s="3">
         <v>1300</v>
@@ -2891,11 +2960,11 @@
         <v>1300</v>
       </c>
       <c r="Z32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA32" s="3">
         <v>700</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -2909,102 +2978,108 @@
         <v>0</v>
       </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>187800</v>
+      </c>
+      <c r="E33" s="3">
         <v>181800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>200800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>188500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>210100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>260600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>298900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>252200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>215000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>249000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>205500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>165200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>122700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>138100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>56200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>140500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>135200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>178500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>192100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>185400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>203000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>205100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>185200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>139000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>266700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>138000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>142000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>116400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>109700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>187800</v>
+      </c>
+      <c r="E35" s="3">
         <v>181800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>200800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>188500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>210100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>260600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>298900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>252200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>215000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>249000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>205500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>165200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>122700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>138100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>56200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>140500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>135200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>178500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>192100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>185400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>203000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>205100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>185200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>139000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>266700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>138000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>142000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>116400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>109700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,153 +3437,157 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>648000</v>
+      </c>
+      <c r="E41" s="3">
         <v>573200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>477100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>367700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>320000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>648700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>667300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>628600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>618700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1702900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>972200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>983400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>974600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>949100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>853300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>764000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>679500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>738300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>569400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>442400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>361500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>293800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>199600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>102400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>216900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>370500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>321000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>254000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>239300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>279800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>493500</v>
+      </c>
+      <c r="E42" s="3">
         <v>104000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>101900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>95600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>85200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>77700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>82300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>81300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>86100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>88300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>101700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>102500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>105600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>101200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>86900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>92300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>87900</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>8</v>
@@ -3512,8 +3601,8 @@
       <c r="X42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3536,429 +3625,444 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1037500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1045200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1023900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1031400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1067500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1118900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1212000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1140700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1078400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1078100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>981400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>908600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>837500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>864600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>823400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>879500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>872100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>941800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>958400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>930300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>918600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>991300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>936700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>908800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>900200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>851300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>755200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>733300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>703100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>731500</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1013100</v>
+      </c>
+      <c r="E44" s="3">
         <v>986100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>992200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1003400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>977300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>994900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>954200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>941200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>902500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>880100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>827200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>799600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>787900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>777600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>834500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>809900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>794100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>806300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>815700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>831700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>795600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>780600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>763700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>766400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>762500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>736600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>734400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>744500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>723600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>62300</v>
+      </c>
+      <c r="E45" s="3">
         <v>64800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>75500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>87300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>58300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>67300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>74600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>77600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>47000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>55400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>78600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>62800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>44700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>51200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>60900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>67900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>44800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>44900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>59200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>58000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>39400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>49000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>56600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>55000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>35500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>43400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>52800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>47300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>30300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>45100</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3254400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2773300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2670600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2585400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2508300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2907500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2990400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2869400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2732700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3804800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2961100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2856900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2750300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2743700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2659000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2613600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2478400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2531300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2402700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2262400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2115100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2114700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1956600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1832600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1915100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2001800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1863400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1779100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1696300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1747000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E47" s="3">
         <v>49300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>50600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>56900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>64900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>67100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>61200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>68500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>60000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>57800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>49900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>47000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>42700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>45200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>36300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>57100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>58100</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>8</v>
@@ -3972,8 +4076,8 @@
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3996,192 +4100,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4143400</v>
+      </c>
+      <c r="E48" s="3">
         <v>4142400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4172900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4185200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4198300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4100000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4036700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3935100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3767300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3591200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3473500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3444000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3427600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3362600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3344400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3373900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3386000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3342700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3345200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3327100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3108600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3065100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3026500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2961400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2924900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2881600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2872500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2887200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2895700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2878700</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1152000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1161600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1171100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1180700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1190300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1199800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1209800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1221300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1231900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1131200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1140500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1149800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1159400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1168900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1178400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1247900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1257500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1267200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1276900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1286000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1295500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1262600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1272800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1282800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1293200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1079900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1087300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1095900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1105000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1046900</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>67200</v>
+      </c>
+      <c r="E52" s="3">
         <v>51000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>41300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>40800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>70000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>42500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>43500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>44900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>45800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>48600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>51300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>53200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>52200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>53900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>55100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>55800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>49900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>49600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>53100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>50500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>57600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>59700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>63000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>64300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>63900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>80000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>81200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>80000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8681100</v>
+      </c>
+      <c r="E54" s="3">
         <v>8177600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8106500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8049000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8003800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8344400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8340600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8137800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7836800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8630800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7673600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7549000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7433200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7372600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7272000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7347600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7235800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7191100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7074400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6928600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6569700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6500000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6315600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6139800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6197500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6027200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5903200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5843400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5777000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5747200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,108 +4837,112 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>402400</v>
+      </c>
+      <c r="E57" s="3">
         <v>405900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>365800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>410500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>410400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>485300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>528200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>546700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>452400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>499100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>405300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>402500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>387000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>352100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>315200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>389000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>351900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>385500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>382800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>405100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>382200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>438900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>431700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>427300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>402900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>379500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>349200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>367300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>323800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>401600</v>
+      </c>
+      <c r="E58" s="3">
         <v>401500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1900</v>
       </c>
       <c r="F58" s="3">
         <v>1900</v>
@@ -4818,7 +4951,7 @@
         <v>1900</v>
       </c>
       <c r="H58" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="I58" s="3">
         <v>1800</v>
@@ -4827,19 +4960,19 @@
         <v>1800</v>
       </c>
       <c r="K58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L58" s="3">
         <v>1700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>699800</v>
-      </c>
-      <c r="M58" s="3">
-        <v>1700</v>
       </c>
       <c r="N58" s="3">
         <v>1700</v>
       </c>
       <c r="O58" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="P58" s="3">
         <v>1600</v>
@@ -4851,7 +4984,7 @@
         <v>1600</v>
       </c>
       <c r="S58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="T58" s="3">
         <v>1500</v>
@@ -4863,7 +4996,7 @@
         <v>1500</v>
       </c>
       <c r="W58" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="X58" s="3">
         <v>1400</v>
@@ -4875,10 +5008,10 @@
         <v>1400</v>
       </c>
       <c r="AA58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB58" s="3">
         <v>151300</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>157800</v>
       </c>
       <c r="AC58" s="3">
         <v>157800</v>
@@ -4887,208 +5020,217 @@
         <v>157800</v>
       </c>
       <c r="AE58" s="3">
+        <v>157800</v>
+      </c>
+      <c r="AF58" s="3">
         <v>27100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>461700</v>
+      </c>
+      <c r="E59" s="3">
         <v>471500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>430000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>416500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>463200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>476300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>442900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>419400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>430700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>445500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>409800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>401600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>394000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>421700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>366800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>354000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>370400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>383700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>345300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>334100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>310000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>326200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>282700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>244900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>278500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>287000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>253200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>250900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>274500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1265700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1278900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>797700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>828900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>875500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>963400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>972900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>967900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>884800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1644400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>816800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>805800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>782600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>775400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>683600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>744600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>723800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>770700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>729600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>740700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>693600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>766500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>715800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>673600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>832700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>824300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>760200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>776000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>625400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2480900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2085000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2484500</v>
-      </c>
-      <c r="F61" s="3">
-        <v>2484400</v>
       </c>
       <c r="G61" s="3">
         <v>2484400</v>
@@ -5097,10 +5239,10 @@
         <v>2484400</v>
       </c>
       <c r="I61" s="3">
+        <v>2484400</v>
+      </c>
+      <c r="J61" s="3">
         <v>2484300</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2484200</v>
       </c>
       <c r="K61" s="3">
         <v>2484200</v>
@@ -5109,159 +5251,165 @@
         <v>2484200</v>
       </c>
       <c r="M61" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="N61" s="3">
         <v>2493300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2494000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2493800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2493500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2493200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2493000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2492800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2502700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2502200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2501800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2501300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2500800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2500400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2499800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2499400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2475600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2477000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2478400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2640300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2646500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>937200</v>
+      </c>
+      <c r="E62" s="3">
         <v>926500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>975700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>978000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>976800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>925400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>918900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>906400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>860600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>893900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>919200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>918000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>910500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>898300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>962100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>960100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>948200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>883000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>921400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>891500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>702400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>702500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>711400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>692600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>682800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>733100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>759400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>764300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>751500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>733200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4683800</v>
+      </c>
+      <c r="E66" s="3">
         <v>4290400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4257900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4291300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4336700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4373200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4376100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4358500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4229600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5022500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4229300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4217800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4186900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4167200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4138900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4197700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4164800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4156400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4153200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4134000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3897300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3969800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3927600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3866000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4014900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4033000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3996600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4018700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4017200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4017600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3447200</v>
+      </c>
+      <c r="E72" s="3">
         <v>3370500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3339000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3259300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3186800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3443500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3437000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3261900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3102100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3162800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3008500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2906300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2835500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2806700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2742900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2771100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2704800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2643700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2539200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2427800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2315800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2185500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2054000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1949600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1867400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1658200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1578800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1504500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1447100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1396900</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3997300</v>
+      </c>
+      <c r="E76" s="3">
         <v>3887200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3848600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3757700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3667100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3971200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3964500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3779300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3607200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3608300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3444300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3331200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3246300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3205400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3133100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3149900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3071000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3034700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2921200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2794600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2672400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2530200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2388000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2273800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2182600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1994200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1906600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1824700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1759800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1729600</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>187800</v>
+      </c>
+      <c r="E81" s="3">
         <v>181800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>200800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>188500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>210100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>260600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>298900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>252200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>215000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>249000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>205500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>165200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>122700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>138100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>56200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>140500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>135200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>178500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>192100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>185400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>203000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>205100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>185200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>139000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>266700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>138000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>142000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>116400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>109700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>130900</v>
+      </c>
+      <c r="E83" s="3">
         <v>129400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>127900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>129500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>118800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>114000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>114300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>109700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>106400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>105600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>104700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>100500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>108200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>100300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>98900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>97900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>95900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>94800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>97300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>101400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>104100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>108100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>107700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>97500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>93700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>92500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>93700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>335300</v>
+      </c>
+      <c r="E89" s="3">
         <v>339500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>359900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>280400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>420100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>430600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>319000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>325300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>390700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>283600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>228200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>191600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>271100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>298200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>226800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>236700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>329200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>339800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>302400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>236000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>345600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>301000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>331000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>202500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>272800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>197700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>221500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>164100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>213400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>217300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-141200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-90100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-127000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-114000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-247500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-182800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-184500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-215600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-238900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-149900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-60700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-174400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-139000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-544000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-88900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-126800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-115400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-251800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-183800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-176900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-221200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-429400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-144800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-132700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-87500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-170200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-127100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-51800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-77000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-278300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-95500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-92700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-80100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-202900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-131800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-166300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-381500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-86700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-83100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-57800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-186900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-455000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,34 +8117,35 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-112400</v>
+        <v>-112000</v>
       </c>
       <c r="E96" s="3">
         <v>-112400</v>
       </c>
       <c r="F96" s="3">
+        <v>-112400</v>
+      </c>
+      <c r="G96" s="3">
         <v>-112100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-115900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-117200</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-93600</v>
       </c>
       <c r="J96" s="3">
         <v>-93600</v>
       </c>
       <c r="K96" s="3">
-        <v>-95000</v>
+        <v>-93600</v>
       </c>
       <c r="L96" s="3">
         <v>-95000</v>
@@ -7921,43 +8154,43 @@
         <v>-95000</v>
       </c>
       <c r="N96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-94800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-75000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-74900</v>
       </c>
       <c r="Q96" s="3">
         <v>-74900</v>
       </c>
       <c r="R96" s="3">
-        <v>-74800</v>
+        <v>-74900</v>
       </c>
       <c r="S96" s="3">
         <v>-74800</v>
       </c>
       <c r="T96" s="3">
-        <v>-74600</v>
+        <v>-74800</v>
       </c>
       <c r="U96" s="3">
         <v>-74600</v>
       </c>
       <c r="V96" s="3">
-        <v>-74700</v>
+        <v>-74600</v>
       </c>
       <c r="W96" s="3">
         <v>-74700</v>
       </c>
       <c r="X96" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-74500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-59500</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-59400</v>
       </c>
       <c r="AA96" s="3">
         <v>-59400</v>
@@ -7975,10 +8208,13 @@
         <v>-59400</v>
       </c>
       <c r="AF96" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,67 +8495,70 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>283500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-154500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-123700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-117300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-497000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-265400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-103400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-94200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1045500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>591900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-106700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-95300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-75400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-75300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-85700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-75200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-109700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-75400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-82700</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-75000</v>
       </c>
       <c r="W100" s="3">
         <v>-75000</v>
@@ -8322,31 +8567,34 @@
         <v>-75000</v>
       </c>
       <c r="Y100" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-67500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-209800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-44900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-91600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E102" s="3">
         <v>96100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>109400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>47700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-328700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>38700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1084200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>730700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>95800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>89300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>84500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-58800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>168900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>127000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>80900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>67700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>94200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>97200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-114500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-153600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>49500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>67000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>14700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-40500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>66200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>PKG</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1979500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1937900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1936000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1952100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1976300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1978400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2125900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2237300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2136400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2043200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2000100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1879900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1807200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1714200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1693700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1541600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1708700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1720000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1750700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1759900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1733700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1746500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1809900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1767500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1690600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1684300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1640100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1584000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1536500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1476600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1484000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1609100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1527800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1523300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1507400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1544900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1528100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1607500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1648500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1603200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1533300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1489400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1431100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1403500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1380900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1348300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1209700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1342900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1336700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1339300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1332000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1312300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1321100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1366700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1346900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1334500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1312600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1242800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1219400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1198000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1149500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1154500</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>370400</v>
+      </c>
+      <c r="E10" s="3">
         <v>410100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>412700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>444700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>431400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>450300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>518400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>588800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>533200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>509900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>510700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>448800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>403700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>333300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>345400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>331900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>365800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>383300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>411400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>427900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>421400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>425400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>443200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>420600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>356100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>371700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>397300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>364600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>338500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>327100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>329500</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,103 +1318,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E14" s="3">
         <v>1200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>58000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-3100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>74600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>7200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>21500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>3500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>6000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1783500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1676400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1677400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1667700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1705600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1690400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1765600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1821500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1779900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1745900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1647800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1585300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1568900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1525000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1484200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1425500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1499600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1484900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1487900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1479500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1458300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1459800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1511400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1497900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1477700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1432300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1397800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1350200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1333400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1283700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1277600</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>196000</v>
+      </c>
+      <c r="E18" s="3">
         <v>261500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>258600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>284400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>270700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>288000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>360300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>415800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>356500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>297300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>352300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>294600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>238300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>189200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>209500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>116100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>209100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>235100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>262800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>280400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>275400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>286700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>298500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>269600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>212900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>252000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>242300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>233800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>203100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>192900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>206400</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,25 +1781,26 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-2000</v>
       </c>
       <c r="G20" s="3">
         <v>-2000</v>
       </c>
       <c r="H20" s="3">
-        <v>3600</v>
+        <v>-2000</v>
       </c>
       <c r="I20" s="3">
         <v>3600</v>
@@ -1778,19 +1812,19 @@
         <v>3600</v>
       </c>
       <c r="L20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M20" s="3">
         <v>4900</v>
-      </c>
-      <c r="M20" s="3">
-        <v>5000</v>
       </c>
       <c r="N20" s="3">
         <v>5000</v>
       </c>
       <c r="O20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="P20" s="3">
         <v>4800</v>
-      </c>
-      <c r="P20" s="3">
-        <v>600</v>
       </c>
       <c r="Q20" s="3">
         <v>600</v>
@@ -1802,19 +1836,19 @@
         <v>600</v>
       </c>
       <c r="T20" s="3">
+        <v>600</v>
+      </c>
+      <c r="U20" s="3">
         <v>-3100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-3300</v>
       </c>
       <c r="W20" s="3">
         <v>-3300</v>
       </c>
       <c r="X20" s="3">
-        <v>-1300</v>
+        <v>-3300</v>
       </c>
       <c r="Y20" s="3">
         <v>-1300</v>
@@ -1823,11 +1857,11 @@
         <v>-1300</v>
       </c>
       <c r="AA20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-700</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1841,390 +1875,405 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-23400</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>325500</v>
+      </c>
+      <c r="E21" s="3">
         <v>390500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>386200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>410300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>398200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>410400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>477900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>533700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>469800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>408600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>462900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>404300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>343900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>290700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>310600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>224900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>310000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>330900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>357500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>373000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>366900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>382700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>398600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>372400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>320300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>359700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>339800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>327500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>295600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>286600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E22" s="3">
         <v>11100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>15100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>21800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23500</v>
-      </c>
-      <c r="P22" s="3">
-        <v>24400</v>
       </c>
       <c r="Q22" s="3">
         <v>24400</v>
       </c>
       <c r="R22" s="3">
+        <v>24400</v>
+      </c>
+      <c r="S22" s="3">
         <v>25100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>59600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>20300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>22800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>25600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>28000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24300</v>
       </c>
-      <c r="AG22" s="3" t="s">
+      <c r="AH22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>187500</v>
+      </c>
+      <c r="E23" s="3">
         <v>248500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>244500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>267800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>253300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>276500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>347400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>400600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>340300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>280400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>333900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>274700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>219600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>165400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>185700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>91600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>190100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>172400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>239300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>256000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>249300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>264500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>274100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>245300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>186600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>224000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>216900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>208600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>179100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>168600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E24" s="3">
         <v>59300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>61300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>65100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>63200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>64900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>84900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>99100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>86100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>63900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>83200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>67400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>53100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>41800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>46600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>34900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>48400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>36200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>59500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>62400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>62500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>61900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>67400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>58700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>46500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>77200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>77800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>65400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>61700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>57900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>63700</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>146900</v>
+      </c>
+      <c r="E26" s="3">
         <v>189200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>183200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>202700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>190100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>211600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>262500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>301500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>254200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>216500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>250700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>207300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>166500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>123600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>139100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>56700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>141700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>136200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>179800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>193600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>186800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>202600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>206700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>186600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>140100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>146800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>139100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>143200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>117400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>110700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>145900</v>
+      </c>
+      <c r="E27" s="3">
         <v>187800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>181800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>200800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>188500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>210100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>260600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>298900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>252200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>215000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>249000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>205500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>165200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>122700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>138100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>56200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>140500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>135200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>178500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>192100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>185400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>201000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>205100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>185200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>139000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>144600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>138000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>142000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>116400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>109700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2650,8 +2711,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2668,11 +2729,11 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>2000</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2680,11 +2741,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>122100</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,25 +2955,28 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2000</v>
       </c>
       <c r="G32" s="3">
         <v>2000</v>
       </c>
       <c r="H32" s="3">
-        <v>-3600</v>
+        <v>2000</v>
       </c>
       <c r="I32" s="3">
         <v>-3600</v>
@@ -2918,19 +2988,19 @@
         <v>-3600</v>
       </c>
       <c r="L32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="M32" s="3">
         <v>-4900</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-5000</v>
       </c>
       <c r="N32" s="3">
         <v>-5000</v>
       </c>
       <c r="O32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="P32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-600</v>
       </c>
       <c r="Q32" s="3">
         <v>-600</v>
@@ -2942,19 +3012,19 @@
         <v>-600</v>
       </c>
       <c r="T32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U32" s="3">
         <v>3100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>3300</v>
       </c>
       <c r="W32" s="3">
         <v>3300</v>
       </c>
       <c r="X32" s="3">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="Y32" s="3">
         <v>1300</v>
@@ -2963,11 +3033,11 @@
         <v>1300</v>
       </c>
       <c r="AA32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB32" s="3">
         <v>700</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -2981,105 +3051,111 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>145900</v>
+      </c>
+      <c r="E33" s="3">
         <v>187800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>181800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>200800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>188500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>210100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>260600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>298900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>252200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>215000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>249000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>205500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>165200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>122700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>138100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>56200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>140500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>135200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>178500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>192100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>185400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>203000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>205100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>185200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>139000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>266700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>138000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>142000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>116400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>109700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>145900</v>
+      </c>
+      <c r="E35" s="3">
         <v>187800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>181800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>200800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>188500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>210100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>260600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>298900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>252200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>215000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>249000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>205500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>165200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>122700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>138100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>56200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>140500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>135200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>178500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>192100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>185400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>203000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>205100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>185200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>139000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>266700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>138000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>142000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>116400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>109700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,159 +3524,163 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>692400</v>
+      </c>
+      <c r="E41" s="3">
         <v>648000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>573200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>477100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>367700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>320000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>648700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>667300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>628600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>618700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1702900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>972200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>983400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>974600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>949100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>853300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>764000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>679500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>738300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>569400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>442400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>361500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>293800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>199600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>102400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>216900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>370500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>321000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>254000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>239300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>279800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>492300</v>
+      </c>
+      <c r="E42" s="3">
         <v>493500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>104000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>101900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>95600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>85200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>77700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>82300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>81300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>86100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>88300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>101700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>102500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>105600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>101200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>86900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>92300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>87900</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>8</v>
@@ -3604,8 +3694,8 @@
       <c r="Y42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3628,444 +3718,459 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1045100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1037500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1045200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1023900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1031400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1067500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1118900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1212000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1140700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1078400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1078100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>981400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>908600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>837500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>864600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>823400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>879500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>872100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>941800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>958400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>930300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>918600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>991300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>936700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>908800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>900200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>851300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>755200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>733300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>703100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>731500</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1003600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1013100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>986100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>992200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1003400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>977300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>994900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>954200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>941200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>902500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>880100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>827200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>799600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>787900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>777600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>834500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>809900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>794100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>806300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>815700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>831700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>795600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>780600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>763700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>766400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>762500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>736600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>734400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>744500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>723600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>211700</v>
+      </c>
+      <c r="E45" s="3">
         <v>62300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>64800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>75500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>87300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>58300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>67300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>74600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>77600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>47000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>55400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>78600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>62800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>44700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>51200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>60900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>67900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>44800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>44900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>59200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>58000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>39400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>49000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>56600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>55000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>35500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>43400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>52800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>47300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>30300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>45100</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3445100</v>
+      </c>
+      <c r="E46" s="3">
         <v>3254400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2773300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2670600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2585400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2508300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2907500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2990400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2869400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2732700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3804800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2961100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2856900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2750300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2743700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2659000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2613600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2478400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2531300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2402700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2262400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2115100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2114700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1956600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1832600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1915100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2001800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1863400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1779100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1696300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1747000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E47" s="3">
         <v>64100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>49300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>50600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>56900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>64900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>67100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>61200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>68500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>60000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>57800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>49900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>47000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>42700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>45200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>36300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>57100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>58100</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>8</v>
@@ -4079,8 +4184,8 @@
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -4103,198 +4208,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4133900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4143400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4142400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4172900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4185200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4198300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4100000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4036700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3935100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3767300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3591200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3473500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3444000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3427600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3362600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3344400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3373900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3386000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3342700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3345200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3327100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3108600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3065100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3026500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2961400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2924900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2881600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2872500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2887200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2895700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2878700</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1142500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1152000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1161600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1171100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1180700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1190300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1199800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1209800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1221300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1231900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1131200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1140500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1149800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1159400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1168900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1178400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1247900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1257500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1267200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1276900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1286000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1295500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1262600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1272800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1282800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1293200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1079900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1087300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1095900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1105000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1046900</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E52" s="3">
         <v>67200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>51000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>41300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>40800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>42000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>70000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>42500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>43500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>44900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>45800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>48600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>51300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>53200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>52200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>53900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>55100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>55800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>49900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>49600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>53100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>50500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>57600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>59700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>63000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>64300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>63900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>80000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>81200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>80000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8857000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8681100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8177600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8106500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8049000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8003800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8344400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8340600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8137800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7836800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8630800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7673600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7549000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7433200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7372600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7272000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7347600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7235800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7191100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7074400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6928600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6569700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6500000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6315600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6139800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6197500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6027200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5903200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5843400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5777000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5747200</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,114 +4968,118 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>449600</v>
+      </c>
+      <c r="E57" s="3">
         <v>402400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>405900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>365800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>410500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>410400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>485300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>528200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>546700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>452400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>499100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>405300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>402500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>387000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>352100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>315200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>389000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>351900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>385500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>382800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>405100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>382200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>438900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>431700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>427300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>402900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>379500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>349200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>367300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>323800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>401800</v>
+      </c>
+      <c r="E58" s="3">
         <v>401600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>401500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1900</v>
       </c>
       <c r="G58" s="3">
         <v>1900</v>
@@ -4954,7 +5088,7 @@
         <v>1900</v>
       </c>
       <c r="I58" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="J58" s="3">
         <v>1800</v>
@@ -4963,19 +5097,19 @@
         <v>1800</v>
       </c>
       <c r="L58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M58" s="3">
         <v>1700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>699800</v>
-      </c>
-      <c r="N58" s="3">
-        <v>1700</v>
       </c>
       <c r="O58" s="3">
         <v>1700</v>
       </c>
       <c r="P58" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="Q58" s="3">
         <v>1600</v>
@@ -4987,7 +5121,7 @@
         <v>1600</v>
       </c>
       <c r="T58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="U58" s="3">
         <v>1500</v>
@@ -4999,7 +5133,7 @@
         <v>1500</v>
       </c>
       <c r="X58" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="Y58" s="3">
         <v>1400</v>
@@ -5011,10 +5145,10 @@
         <v>1400</v>
       </c>
       <c r="AB58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC58" s="3">
         <v>151300</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>157800</v>
       </c>
       <c r="AD58" s="3">
         <v>157800</v>
@@ -5023,217 +5157,226 @@
         <v>157800</v>
       </c>
       <c r="AF58" s="3">
+        <v>157800</v>
+      </c>
+      <c r="AG58" s="3">
         <v>27100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>548900</v>
+      </c>
+      <c r="E59" s="3">
         <v>461700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>471500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>430000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>416500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>463200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>476300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>442900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>419400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>430700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>445500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>409800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>401600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>394000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>421700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>366800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>354000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>370400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>383700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>345300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>334100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>310000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>326200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>282700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>244900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>278500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>287000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>253200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>250900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>274500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1400300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1265700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1278900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>797700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>828900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>875500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>963400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>972900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>967900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>884800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1644400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>816800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>805800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>782600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>775400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>683600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>744600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>723800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>770700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>729600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>740700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>693600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>766500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>715800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>673600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>832700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>824300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>760200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>776000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>625400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2481000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2480900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2085000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2484500</v>
-      </c>
-      <c r="G61" s="3">
-        <v>2484400</v>
       </c>
       <c r="H61" s="3">
         <v>2484400</v>
@@ -5242,10 +5385,10 @@
         <v>2484400</v>
       </c>
       <c r="J61" s="3">
+        <v>2484400</v>
+      </c>
+      <c r="K61" s="3">
         <v>2484300</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2484200</v>
       </c>
       <c r="L61" s="3">
         <v>2484200</v>
@@ -5254,162 +5397,168 @@
         <v>2484200</v>
       </c>
       <c r="N61" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="O61" s="3">
         <v>2493300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2494000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2493800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2493500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2493200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2493000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2492800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2502700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2502200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2501800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2501300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2500800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2500400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2499800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2499400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2475600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2477000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2478400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2640300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2646500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>944700</v>
+      </c>
+      <c r="E62" s="3">
         <v>937200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>926500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>975700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>978000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>976800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>925400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>918900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>906400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>860600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>893900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>919200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>918000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>910500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>898300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>962100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>960100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>948200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>883000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>921400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>891500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>702400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>702500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>711400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>692600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>682800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>733100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>759400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>764300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>751500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>733200</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4826000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4683800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4290400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4257900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4291300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4336700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4373200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4376100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4358500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4229600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5022500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4229300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4217800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4186900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4167200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4138900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4197700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4164800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4156400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4153200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4134000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3897300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3969800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3927600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3866000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4014900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4033000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3996600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4018700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4017200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4017600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3459600</v>
+      </c>
+      <c r="E72" s="3">
         <v>3447200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3370500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3339000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3259300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3186800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3443500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3437000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3261900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3102100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3162800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3008500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2906300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2835500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2806700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2742900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2771100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2704800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2643700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2539200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2427800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2315800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2185500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2054000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1949600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1867400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1658200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1578800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1504500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1447100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1396900</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4031000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3997300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3887200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3848600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3757700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3667100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3971200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3964500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3779300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3607200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3608300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3444300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3331200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3246300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3205400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3133100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3149900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3071000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3034700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2921200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2794600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2672400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2530200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2388000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2273800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2182600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1994200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1906600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1824700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1759800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1729600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>145900</v>
+      </c>
+      <c r="E81" s="3">
         <v>187800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>181800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>200800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>188500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>210100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>260600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>298900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>252200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>215000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>249000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>205500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>165200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>122700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>138100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>56200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>140500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>135200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>178500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>192100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>185400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>203000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>205100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>185200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>139000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>266700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>138000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>142000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>116400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>109700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>128400</v>
+      </c>
+      <c r="E83" s="3">
         <v>130900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>129400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>127900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>129500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>118800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>114000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>114300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>109700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>106400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>105600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>104700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>100900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>108200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>100300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>98900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>97900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>95900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>94800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>97300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>101400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>104100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>108100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>107700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>97500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>93700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>92500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>93700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>260400</v>
+      </c>
+      <c r="E89" s="3">
         <v>335300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>339500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>359900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>280400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>420100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>430600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>319000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>325300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>390700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>283600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>228200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>191600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>271100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>298200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>226800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>236700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>329200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>339800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>302400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>236000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>345600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>301000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>331000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>202500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>272800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>197700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>221500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>164100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>213400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>217300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-78100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-141200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-90100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-127000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-114000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-247500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-182800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-184500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-215600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-238900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-149900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-60700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-174400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-139000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-544000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-88900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-126800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-115400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-251800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-183800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-176900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-221200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-429400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-144800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-132700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-87500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-170200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-127100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-51800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-77000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-278300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-95500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-92700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-80100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-202900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-131800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-166300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-381500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-86700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-83100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-57800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-186900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-455000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8127,28 +8361,28 @@
         <v>-112000</v>
       </c>
       <c r="E96" s="3">
-        <v>-112400</v>
+        <v>-112000</v>
       </c>
       <c r="F96" s="3">
         <v>-112400</v>
       </c>
       <c r="G96" s="3">
+        <v>-112400</v>
+      </c>
+      <c r="H96" s="3">
         <v>-112100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-115900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-117200</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-93600</v>
       </c>
       <c r="K96" s="3">
         <v>-93600</v>
       </c>
       <c r="L96" s="3">
-        <v>-95000</v>
+        <v>-93600</v>
       </c>
       <c r="M96" s="3">
         <v>-95000</v>
@@ -8157,43 +8391,43 @@
         <v>-95000</v>
       </c>
       <c r="O96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-94800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-75000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-74900</v>
       </c>
       <c r="R96" s="3">
         <v>-74900</v>
       </c>
       <c r="S96" s="3">
-        <v>-74800</v>
+        <v>-74900</v>
       </c>
       <c r="T96" s="3">
         <v>-74800</v>
       </c>
       <c r="U96" s="3">
-        <v>-74600</v>
+        <v>-74800</v>
       </c>
       <c r="V96" s="3">
         <v>-74600</v>
       </c>
       <c r="W96" s="3">
-        <v>-74700</v>
+        <v>-74600</v>
       </c>
       <c r="X96" s="3">
         <v>-74700</v>
       </c>
       <c r="Y96" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-74500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-59500</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-59400</v>
       </c>
       <c r="AB96" s="3">
         <v>-59400</v>
@@ -8211,10 +8445,13 @@
         <v>-59400</v>
       </c>
       <c r="AG96" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,70 +8741,73 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-135000</v>
+      </c>
+      <c r="E100" s="3">
         <v>283500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-154500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-123700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-117300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-497000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-265400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-103400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-94200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1045500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>591900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-106700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-95300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-75400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-75300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-85700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-75200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-109700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-75400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-82700</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-75000</v>
       </c>
       <c r="X100" s="3">
         <v>-75000</v>
@@ -8570,31 +8816,34 @@
         <v>-75000</v>
       </c>
       <c r="Z100" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-67500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-209800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-44900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-91600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E102" s="3">
         <v>74800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>96100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>109400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>47700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-328700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>38700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1084200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>730700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>95800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>89300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>84500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-58800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>168900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>127000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>80900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>67700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>94200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>97200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-114500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-153600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>49500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>67000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>14700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-40500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>66200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>PKG</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2075300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1979500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1937900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1936000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1952100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1976300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1978400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2125900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2237300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2136400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2043200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2000100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1879900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1807200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1714200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1693700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1541600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1708700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1720000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1750700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1759900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1733700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1746500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1809900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1767500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1690600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1684300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1640100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1584000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1536500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1476600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1484000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1637600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1609100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1527800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1523300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1507400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1544900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1528100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1607500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1648500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1603200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1533300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1489400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1431100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1403500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1380900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1348300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1209700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1342900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1336700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1339300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1332000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1312300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1321100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1366700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1346900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1334500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1312600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1242800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1219400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1198000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1149500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1154500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>437700</v>
+      </c>
+      <c r="E10" s="3">
         <v>370400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>410100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>412700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>444700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>431400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>450300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>518400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>588800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>533200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>509900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>510700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>448800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>403700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>333300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>345400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>331900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>365800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>383300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>411400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>427900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>421400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>425400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>443200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>420600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>356100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>371700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>397300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>364600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>338500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>327100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>329500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,106 +1338,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E14" s="3">
         <v>8200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>58000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-3100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>74600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>7200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>21500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>6000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1799300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1783500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1676400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1677400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1667700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1705600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1690400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1765600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1821500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1779900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1745900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1647800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1585300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1568900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1525000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1484200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1425500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1499600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1484900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1487900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1479500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1458300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1459800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1511400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1497900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1477700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1432300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1397800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1350200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1333400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1283700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1277600</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E18" s="3">
         <v>196000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>261500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>258600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>284400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>270700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>288000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>360300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>415800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>356500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>297300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>352300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>294600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>238300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>189200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>209500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>116100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>209100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>235100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>262800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>280400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>275400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>286700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>298500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>269600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>212900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>252000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>242300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>233800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>203100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>192900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>206400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1791,19 +1825,19 @@
         <v>1100</v>
       </c>
       <c r="E20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2000</v>
       </c>
       <c r="H20" s="3">
         <v>-2000</v>
       </c>
       <c r="I20" s="3">
-        <v>3600</v>
+        <v>-2000</v>
       </c>
       <c r="J20" s="3">
         <v>3600</v>
@@ -1815,19 +1849,19 @@
         <v>3600</v>
       </c>
       <c r="M20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="N20" s="3">
         <v>4900</v>
-      </c>
-      <c r="N20" s="3">
-        <v>5000</v>
       </c>
       <c r="O20" s="3">
         <v>5000</v>
       </c>
       <c r="P20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="Q20" s="3">
         <v>4800</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>600</v>
       </c>
       <c r="R20" s="3">
         <v>600</v>
@@ -1839,19 +1873,19 @@
         <v>600</v>
       </c>
       <c r="U20" s="3">
+        <v>600</v>
+      </c>
+      <c r="V20" s="3">
         <v>-3100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-3300</v>
       </c>
       <c r="X20" s="3">
         <v>-3300</v>
       </c>
       <c r="Y20" s="3">
-        <v>-1300</v>
+        <v>-3300</v>
       </c>
       <c r="Z20" s="3">
         <v>-1300</v>
@@ -1860,11 +1894,11 @@
         <v>-1300</v>
       </c>
       <c r="AB20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-700</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -1878,402 +1912,417 @@
         <v>0</v>
       </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-23400</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>405600</v>
+      </c>
+      <c r="E21" s="3">
         <v>325500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>390500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>386200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>410300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>398200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>410400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>477900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>533700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>469800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>408600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>462900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>404300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>343900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>290700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>310600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>224900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>310000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>330900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>357500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>373000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>366900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>382700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>398600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>372400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>320300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>359700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>339800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>327500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>295600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>286600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E22" s="3">
         <v>9600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>15400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>18800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>19800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>21800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>23400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>24900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23500</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>24400</v>
       </c>
       <c r="R22" s="3">
         <v>24400</v>
       </c>
       <c r="S22" s="3">
+        <v>24400</v>
+      </c>
+      <c r="T22" s="3">
         <v>25100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>59600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>20300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>22800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>25600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>28000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>25200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>24300</v>
       </c>
-      <c r="AH22" s="3" t="s">
+      <c r="AI22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>266700</v>
+      </c>
+      <c r="E23" s="3">
         <v>187500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>248500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>244500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>267800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>253300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>276500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>347400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>400600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>340300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>280400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>333900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>274700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>219600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>165400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>185700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>91600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>190100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>172400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>239300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>256000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>249300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>264500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>274100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>245300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>186600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>224000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>216900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>208600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>179100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>168600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E24" s="3">
         <v>40600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>59300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>61300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>65100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>63200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>64900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>84900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>99100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>86100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>63900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>83200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>67400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>53100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>41800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>46600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>34900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>48400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>36200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>59500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>62400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>62500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>61900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>67400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>58700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>46500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>77200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>77800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>65400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>61700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>57900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>63700</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>198900</v>
+      </c>
+      <c r="E26" s="3">
         <v>146900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>189200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>183200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>202700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>190100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>211600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>262500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>301500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>254200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>216500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>250700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>207300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>166500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>123600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>139100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>56700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>141700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>136200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>179800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>193600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>186800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>202600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>206700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>186600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>140100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>146800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>139100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>143200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>117400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>110700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>197500</v>
+      </c>
+      <c r="E27" s="3">
         <v>145900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>187800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>181800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>200800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>188500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>210100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>260600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>298900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>252200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>215000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>249000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>205500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>165200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>122700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>138100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>56200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>140500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>135200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>178500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>192100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>185400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>201000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>205100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>185200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>139000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>144600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>138000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>142000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>116400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>109700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2714,8 +2775,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2732,11 +2793,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>2000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2744,11 +2805,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>122100</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2967,19 +3037,19 @@
         <v>-1100</v>
       </c>
       <c r="E32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F32" s="3">
         <v>1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1800</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2000</v>
       </c>
       <c r="H32" s="3">
         <v>2000</v>
       </c>
       <c r="I32" s="3">
-        <v>-3600</v>
+        <v>2000</v>
       </c>
       <c r="J32" s="3">
         <v>-3600</v>
@@ -2991,19 +3061,19 @@
         <v>-3600</v>
       </c>
       <c r="M32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="N32" s="3">
         <v>-4900</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-5000</v>
       </c>
       <c r="O32" s="3">
         <v>-5000</v>
       </c>
       <c r="P32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-600</v>
       </c>
       <c r="R32" s="3">
         <v>-600</v>
@@ -3015,19 +3085,19 @@
         <v>-600</v>
       </c>
       <c r="U32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V32" s="3">
         <v>3100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>3300</v>
       </c>
       <c r="X32" s="3">
         <v>3300</v>
       </c>
       <c r="Y32" s="3">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="Z32" s="3">
         <v>1300</v>
@@ -3036,11 +3106,11 @@
         <v>1300</v>
       </c>
       <c r="AB32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AC32" s="3">
         <v>700</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3054,108 +3124,114 @@
         <v>0</v>
       </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>197500</v>
+      </c>
+      <c r="E33" s="3">
         <v>145900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>187800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>181800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>200800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>188500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>210100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>260600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>298900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>252200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>215000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>249000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>205500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>165200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>122700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>138100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>56200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>140500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>135200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>178500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>192100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>185400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>203000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>205100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>185200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>139000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>266700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>138000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>142000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>116400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>109700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>197500</v>
+      </c>
+      <c r="E35" s="3">
         <v>145900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>187800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>181800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>200800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>188500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>210100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>260600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>298900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>252200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>215000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>249000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>205500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>165200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>122700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>138100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>56200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>140500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>135200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>178500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>192100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>185400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>203000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>205100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>185200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>139000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>266700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>138000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>142000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>116400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>109700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,165 +3611,169 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>613600</v>
+      </c>
+      <c r="E41" s="3">
         <v>692400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>648000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>573200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>477100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>367700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>320000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>648700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>667300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>628600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>618700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1702900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>972200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>983400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>974600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>949100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>853300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>764000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>679500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>738300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>569400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>442400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>361500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>293800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>199600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>102400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>216900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>370500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>321000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>254000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>239300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>279800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>490800</v>
+      </c>
+      <c r="E42" s="3">
         <v>492300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>493500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>104000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>101900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>95600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>85200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>77700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>82300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>81300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>86100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>88300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>101700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>102500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>105600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>101200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>86900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>92300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>87900</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>8</v>
@@ -3697,8 +3787,8 @@
       <c r="Z42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3721,459 +3811,474 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1145500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1045100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1037500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1045200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1023900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1031400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1067500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1118900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1212000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1140700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1078400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1078100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>981400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>908600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>837500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>864600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>823400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>879500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>872100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>941800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>958400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>930300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>918600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>991300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>936700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>908800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>900200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>851300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>755200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>733300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>703100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>731500</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1029500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1003600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1013100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>986100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>992200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1003400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>977300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>994900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>954200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>941200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>902500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>880100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>827200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>799600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>787900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>777600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>834500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>809900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>794100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>806300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>815700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>831700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>795600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>780600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>763700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>766400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>762500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>736600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>734400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>744500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>723600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>204500</v>
+      </c>
+      <c r="E45" s="3">
         <v>211700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>62300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>64800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>75500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>87300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>58300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>67300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>74600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>77600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>47000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>55400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>78600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>62800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>44700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>51200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>60900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>67900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>44800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>44900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>59200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>58000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>39400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>49000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>56600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>55000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>35500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>43400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>52800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>47300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>30300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>45100</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3483900</v>
+      </c>
+      <c r="E46" s="3">
         <v>3445100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3254400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2773300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2670600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2585400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2508300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2907500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2990400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2869400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2732700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3804800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2961100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2856900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2750300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2743700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2659000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2613600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2478400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2531300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2402700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2262400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2115100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2114700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1956600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1832600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1915100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2001800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1863400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1779100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1696300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1747000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E47" s="3">
         <v>68500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>64100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>49300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>50600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>56900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>64900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>67100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>61200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>68500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>60000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>57800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>49900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>47000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>42700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>45200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>36300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>57100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>58100</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>8</v>
@@ -4187,8 +4292,8 @@
       <c r="Z47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -4211,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4228300</v>
+      </c>
+      <c r="E48" s="3">
         <v>4133900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4143400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4142400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4172900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4185200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4198300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4100000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4036700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3935100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3767300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3591200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3473500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3444000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3427600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3362600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3344400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3373900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3386000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3342700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3345200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3327100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3108600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3065100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3026500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2961400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2924900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2881600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2872500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2887200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2895700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2878700</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1133100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1142500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1152000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1161600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1171100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1180700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1190300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1199800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1209800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1221300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1231900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1131200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1140500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1149800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1159400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1168900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1178400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1247900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1257500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1267200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1276900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1286000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1295500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1262600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1272800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1282800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1293200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1079900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1087300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1095900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1105000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1046900</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E52" s="3">
         <v>67000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>67200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>51000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>42000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>70000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>42500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>43500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>44900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>45800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>48600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>51300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>53200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>52200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>53900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>55100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>55800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>49900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>49600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>53100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>50500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>57600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>59700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>63000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>64300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>63900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>80000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>81200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>80000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8982100</v>
+      </c>
+      <c r="E54" s="3">
         <v>8857000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8681100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8177600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8106500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8049000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8003800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8344400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8340600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8137800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7836800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8630800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7673600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7549000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7433200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7372600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7272000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7347600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7235800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7191100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7074400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6928600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6569700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6500000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6315600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6139800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6197500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6027200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5903200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5843400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5777000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5747200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,120 +5099,124 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>474500</v>
+      </c>
+      <c r="E57" s="3">
         <v>449600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>402400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>405900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>365800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>410500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>410400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>485300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>528200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>546700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>452400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>499100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>405300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>402500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>387000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>352100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>315200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>389000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>351900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>385500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>382800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>405100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>382200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>438900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>431700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>427300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>402900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>379500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>349200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>367300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>323800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>402000</v>
+      </c>
+      <c r="E58" s="3">
         <v>401800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>401600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>401500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1900</v>
       </c>
       <c r="H58" s="3">
         <v>1900</v>
@@ -5091,7 +5225,7 @@
         <v>1900</v>
       </c>
       <c r="J58" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="K58" s="3">
         <v>1800</v>
@@ -5100,19 +5234,19 @@
         <v>1800</v>
       </c>
       <c r="M58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N58" s="3">
         <v>1700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>699800</v>
-      </c>
-      <c r="O58" s="3">
-        <v>1700</v>
       </c>
       <c r="P58" s="3">
         <v>1700</v>
       </c>
       <c r="Q58" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="R58" s="3">
         <v>1600</v>
@@ -5124,7 +5258,7 @@
         <v>1600</v>
       </c>
       <c r="U58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="V58" s="3">
         <v>1500</v>
@@ -5136,7 +5270,7 @@
         <v>1500</v>
       </c>
       <c r="Y58" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="Z58" s="3">
         <v>1400</v>
@@ -5148,10 +5282,10 @@
         <v>1400</v>
       </c>
       <c r="AC58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD58" s="3">
         <v>151300</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>157800</v>
       </c>
       <c r="AE58" s="3">
         <v>157800</v>
@@ -5160,226 +5294,235 @@
         <v>157800</v>
       </c>
       <c r="AG58" s="3">
+        <v>157800</v>
+      </c>
+      <c r="AH58" s="3">
         <v>27100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>555000</v>
+      </c>
+      <c r="E59" s="3">
         <v>548900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>461700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>471500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>430000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>416500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>463200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>476300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>442900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>419400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>430700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>445500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>409800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>401600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>394000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>421700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>366800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>354000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>370400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>383700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>345300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>334100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>310000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>326200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>282700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>244900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>278500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>287000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>253200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>250900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>274500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1431500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1400300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1265700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1278900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>797700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>828900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>875500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>963400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>972900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>967900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>884800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1644400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>816800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>805800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>782600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>775400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>683600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>744600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>723800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>770700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>729600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>740700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>693600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>766500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>715800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>673600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>832700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>824300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>760200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>776000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>625400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2480900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2481000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2480900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2085000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2484500</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2484400</v>
       </c>
       <c r="I61" s="3">
         <v>2484400</v>
@@ -5388,10 +5531,10 @@
         <v>2484400</v>
       </c>
       <c r="K61" s="3">
+        <v>2484400</v>
+      </c>
+      <c r="L61" s="3">
         <v>2484300</v>
-      </c>
-      <c r="L61" s="3">
-        <v>2484200</v>
       </c>
       <c r="M61" s="3">
         <v>2484200</v>
@@ -5400,165 +5543,171 @@
         <v>2484200</v>
       </c>
       <c r="O61" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="P61" s="3">
         <v>2493300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2494000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2493800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2493500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2493200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2493000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2492800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2502700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2502200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2501800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2501300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2500800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2500400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2499800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2499400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2475600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2477000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2478400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2640300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2646500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>943100</v>
+      </c>
+      <c r="E62" s="3">
         <v>944700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>937200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>926500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>975700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>978000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>976800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>925400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>918900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>906400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>860600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>893900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>919200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>918000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>910500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>898300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>962100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>960100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>948200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>883000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>921400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>891500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>702400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>702500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>711400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>692600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>682800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>733100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>759400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>764300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>751500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>733200</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4855500</v>
+      </c>
+      <c r="E66" s="3">
         <v>4826000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4683800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4290400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4257900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4291300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4336700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4373200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4376100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4358500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4229600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5022500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4229300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4217800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4186900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4167200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4138900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4197700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4164800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4156400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4153200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4134000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3897300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3969800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3927600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3866000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4014900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4033000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3996600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4018700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4017200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4017600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3544400</v>
+      </c>
+      <c r="E72" s="3">
         <v>3459600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3447200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3370500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3339000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3259300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3186800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3443500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3437000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3261900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3102100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3162800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3008500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2906300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2835500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2806700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2742900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2771100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2704800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2643700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2539200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2427800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2315800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2185500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2054000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1949600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1867400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1658200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1578800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1504500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1447100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1396900</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4126600</v>
+      </c>
+      <c r="E76" s="3">
         <v>4031000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3997300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3887200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3848600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3757700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3667100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3971200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3964500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3779300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3607200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3608300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3444300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3331200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3246300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3205400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3133100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3149900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3071000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3034700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2921200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2794600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2672400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2530200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2388000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2273800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2182600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1994200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1906600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1824700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1759800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1729600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>197500</v>
+      </c>
+      <c r="E81" s="3">
         <v>145900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>187800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>181800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>200800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>188500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>210100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>260600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>298900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>252200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>215000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>249000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>205500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>165200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>122700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>138100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>56200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>140500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>135200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>178500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>192100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>185400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>203000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>205100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>185200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>139000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>266700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>138000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>142000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>116400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>109700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>128500</v>
+      </c>
+      <c r="E83" s="3">
         <v>128400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>130900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>129400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>127900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>129500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>118800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>114000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>114300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>109700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>106400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>105600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>104700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>100800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>100500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>108200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>100300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>98900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>97900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>95900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>94800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>97300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>101400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>104100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>108100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>107700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>97500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>93700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>92500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>93700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>278300</v>
+      </c>
+      <c r="E89" s="3">
         <v>260400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>335300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>339500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>359900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>280400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>420100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>430600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>319000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>325300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>390700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>283600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>228200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>191600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>271100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>298200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>226800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>236700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>329200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>339800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>302400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>236000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>345600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>301000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>331000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>202500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>272800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>197700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>221500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>164100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>213400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>217300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-245300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-78100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-141200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-90100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-127000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-114000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-247500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-182800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-184500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-215600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-238900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-149900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-60700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-174400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-139000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-242800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-81000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-544000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-88900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-126800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-115400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-251800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-183800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-176900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-221200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-429400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-144800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-132700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-87500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-170200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-127100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-51800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-77000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-278300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-95500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-92700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-80100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-202900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-131800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-166300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-381500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-86700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-83100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-57800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-186900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-455000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,40 +8585,41 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-112000</v>
+        <v>-112200</v>
       </c>
       <c r="E96" s="3">
         <v>-112000</v>
       </c>
       <c r="F96" s="3">
-        <v>-112400</v>
+        <v>-112000</v>
       </c>
       <c r="G96" s="3">
         <v>-112400</v>
       </c>
       <c r="H96" s="3">
+        <v>-112400</v>
+      </c>
+      <c r="I96" s="3">
         <v>-112100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-115900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-117200</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-93600</v>
       </c>
       <c r="L96" s="3">
         <v>-93600</v>
       </c>
       <c r="M96" s="3">
-        <v>-95000</v>
+        <v>-93600</v>
       </c>
       <c r="N96" s="3">
         <v>-95000</v>
@@ -8394,43 +8628,43 @@
         <v>-95000</v>
       </c>
       <c r="P96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-94800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-75000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-74900</v>
       </c>
       <c r="S96" s="3">
         <v>-74900</v>
       </c>
       <c r="T96" s="3">
-        <v>-74800</v>
+        <v>-74900</v>
       </c>
       <c r="U96" s="3">
         <v>-74800</v>
       </c>
       <c r="V96" s="3">
-        <v>-74600</v>
+        <v>-74800</v>
       </c>
       <c r="W96" s="3">
         <v>-74600</v>
       </c>
       <c r="X96" s="3">
-        <v>-74700</v>
+        <v>-74600</v>
       </c>
       <c r="Y96" s="3">
         <v>-74700</v>
       </c>
       <c r="Z96" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-74500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-59500</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-59400</v>
       </c>
       <c r="AC96" s="3">
         <v>-59400</v>
@@ -8448,10 +8682,13 @@
         <v>-59400</v>
       </c>
       <c r="AH96" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,73 +8987,76 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-114300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-135000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>283500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-154500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-123700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-117300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-497000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-265400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-103400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-94200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1045500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>591900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-106700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-95300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-75400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-75300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-85700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-75200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-109700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-75400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-82700</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-75000</v>
       </c>
       <c r="Y100" s="3">
         <v>-75000</v>
@@ -8819,31 +9065,34 @@
         <v>-75000</v>
       </c>
       <c r="AA100" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-67500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-209800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-44900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-91600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-78800</v>
+      </c>
+      <c r="E102" s="3">
         <v>44400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>74800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>96100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>109400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>47700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-328700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>38700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1084200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>730700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>25500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>95800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>89300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>84500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-58800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>168900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>127000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>80900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>67700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>94200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>97200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-114500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-153600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>49500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>67000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>14700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-40500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>66200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>PKG</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2182400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2075300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1979500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1937900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1936000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1952100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1976300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1978400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2125900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2237300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2136400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2043200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2000100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1879900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1807200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1714200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1693700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1541600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1708700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1720000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1750700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1759900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1733700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1746500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1809900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1767500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1690600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1684300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1640100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1584000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1536500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1476600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1484000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1677200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1637600</v>
       </c>
-      <c r="E9" s="3">
-        <v>1609100</v>
-      </c>
       <c r="F9" s="3">
-        <v>1527800</v>
+        <v>1607100</v>
       </c>
       <c r="G9" s="3">
-        <v>1523300</v>
+        <v>1524800</v>
       </c>
       <c r="H9" s="3">
-        <v>1507400</v>
+        <v>1520300</v>
       </c>
       <c r="I9" s="3">
-        <v>1544900</v>
+        <v>1504400</v>
       </c>
       <c r="J9" s="3">
+        <v>1538900</v>
+      </c>
+      <c r="K9" s="3">
         <v>1528100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1607500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1648500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1603200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1533300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1489400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1431100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1403500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1380900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1348300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1209700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1342900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1336700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1339300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1332000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1312300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1321100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1366700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1346900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1334500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1312600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1242800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1219400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1198000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1149500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1154500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>505200</v>
+      </c>
+      <c r="E10" s="3">
         <v>437700</v>
       </c>
-      <c r="E10" s="3">
-        <v>370400</v>
-      </c>
       <c r="F10" s="3">
-        <v>410100</v>
+        <v>372400</v>
       </c>
       <c r="G10" s="3">
-        <v>412700</v>
+        <v>413100</v>
       </c>
       <c r="H10" s="3">
-        <v>444700</v>
+        <v>415700</v>
       </c>
       <c r="I10" s="3">
-        <v>431400</v>
+        <v>447700</v>
       </c>
       <c r="J10" s="3">
+        <v>437400</v>
+      </c>
+      <c r="K10" s="3">
         <v>450300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>518400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>588800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>533200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>509900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>510700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>448800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>403700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>333300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>345400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>331900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>365800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>383300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>411400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>427900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>421400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>425400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>443200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>420600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>356100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>371700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>397300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>364600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>338500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>327100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>329500</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,132 +1358,138 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-500</v>
+        <v>11700</v>
       </c>
       <c r="E14" s="3">
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="F14" s="3">
+        <v>17600</v>
+      </c>
+      <c r="G14" s="3">
+        <v>13700</v>
+      </c>
+      <c r="H14" s="3">
+        <v>11900</v>
+      </c>
+      <c r="I14" s="3">
+        <v>13800</v>
+      </c>
+      <c r="J14" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K14" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M14" s="3">
         <v>1200</v>
       </c>
-      <c r="G14" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H14" s="3">
-        <v>4200</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="N14" s="3">
+        <v>400</v>
+      </c>
+      <c r="O14" s="3">
+        <v>58000</v>
+      </c>
+      <c r="P14" s="3">
         <v>4400</v>
       </c>
-      <c r="J14" s="3">
-        <v>2400</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="Q14" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="R14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="S14" s="3">
         <v>2500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="T14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="U14" s="3">
+        <v>74600</v>
+      </c>
+      <c r="V14" s="3">
         <v>1200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="W14" s="3">
+        <v>300</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3">
-        <v>58000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>4400</v>
-      </c>
-      <c r="P14" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>2600</v>
-      </c>
-      <c r="R14" s="3">
-        <v>2500</v>
-      </c>
-      <c r="S14" s="3">
-        <v>2900</v>
-      </c>
-      <c r="T14" s="3">
-        <v>74600</v>
-      </c>
-      <c r="U14" s="3">
-        <v>1200</v>
-      </c>
-      <c r="V14" s="3">
-        <v>300</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>7200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>21500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>3500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>6000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>132500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>128500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>126900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>124500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>126800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>124900</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>123200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1799300</v>
+        <v>1842400</v>
       </c>
       <c r="E17" s="3">
-        <v>1783500</v>
+        <v>1790700</v>
       </c>
       <c r="F17" s="3">
-        <v>1676400</v>
+        <v>1764800</v>
       </c>
       <c r="G17" s="3">
-        <v>1677400</v>
+        <v>1664600</v>
       </c>
       <c r="H17" s="3">
-        <v>1667700</v>
+        <v>1667300</v>
       </c>
       <c r="I17" s="3">
-        <v>1705600</v>
+        <v>1655900</v>
       </c>
       <c r="J17" s="3">
+        <v>1690600</v>
+      </c>
+      <c r="K17" s="3">
         <v>1690400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1765600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1821500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1779900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1745900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1647800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1585300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1568900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1525000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1484200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1425500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1499600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1484900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1487900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1479500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1458300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1459800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1511400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1497900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1477700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1432300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1397800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1350200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1333400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1283700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1277600</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>276000</v>
+        <v>340000</v>
       </c>
       <c r="E18" s="3">
-        <v>196000</v>
+        <v>284600</v>
       </c>
       <c r="F18" s="3">
-        <v>261500</v>
+        <v>214700</v>
       </c>
       <c r="G18" s="3">
-        <v>258600</v>
+        <v>273300</v>
       </c>
       <c r="H18" s="3">
-        <v>284400</v>
+        <v>268700</v>
       </c>
       <c r="I18" s="3">
-        <v>270700</v>
+        <v>296200</v>
       </c>
       <c r="J18" s="3">
+        <v>285700</v>
+      </c>
+      <c r="K18" s="3">
         <v>288000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>360300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>415800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>356500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>297300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>352300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>294600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>238300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>189200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>209500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>116100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>209100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>235100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>262800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>280400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>275400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>286700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>298500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>269600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>212900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>252000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>242300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>233800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>203100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>192900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>206400</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,31 +1849,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>3600</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>3600</v>
@@ -1852,19 +1886,19 @@
         <v>3600</v>
       </c>
       <c r="N20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="O20" s="3">
         <v>4900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>5000</v>
       </c>
       <c r="P20" s="3">
         <v>5000</v>
       </c>
       <c r="Q20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="R20" s="3">
         <v>4800</v>
-      </c>
-      <c r="R20" s="3">
-        <v>600</v>
       </c>
       <c r="S20" s="3">
         <v>600</v>
@@ -1876,19 +1910,19 @@
         <v>600</v>
       </c>
       <c r="V20" s="3">
+        <v>600</v>
+      </c>
+      <c r="W20" s="3">
         <v>-3100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3200</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-3300</v>
       </c>
       <c r="Y20" s="3">
         <v>-3300</v>
       </c>
       <c r="Z20" s="3">
-        <v>-1300</v>
+        <v>-3300</v>
       </c>
       <c r="AA20" s="3">
         <v>-1300</v>
@@ -1897,11 +1931,11 @@
         <v>-1300</v>
       </c>
       <c r="AC20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-700</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
@@ -1915,414 +1949,429 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-23400</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>405600</v>
+        <v>472500</v>
       </c>
       <c r="E21" s="3">
-        <v>325500</v>
+        <v>413100</v>
       </c>
       <c r="F21" s="3">
-        <v>390500</v>
+        <v>341600</v>
       </c>
       <c r="G21" s="3">
-        <v>386200</v>
+        <v>397800</v>
       </c>
       <c r="H21" s="3">
-        <v>410300</v>
+        <v>395500</v>
       </c>
       <c r="I21" s="3">
-        <v>398200</v>
+        <v>421100</v>
       </c>
       <c r="J21" s="3">
+        <v>408900</v>
+      </c>
+      <c r="K21" s="3">
         <v>410400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>477900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>533700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>469800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>408600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>462900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>404300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>343900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>290700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>310600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>224900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>310000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>330900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>357500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>373000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>366900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>382700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>398600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>372400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>320300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>359700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>339800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>327500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>295600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>286600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E22" s="3">
         <v>10400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9600</v>
       </c>
-      <c r="F22" s="3">
-        <v>11100</v>
-      </c>
       <c r="G22" s="3">
+        <v>9500</v>
+      </c>
+      <c r="H22" s="3">
         <v>12300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>15100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>16500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>18800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>19800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>24900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>23500</v>
-      </c>
-      <c r="R22" s="3">
-        <v>24400</v>
       </c>
       <c r="S22" s="3">
         <v>24400</v>
       </c>
       <c r="T22" s="3">
+        <v>24400</v>
+      </c>
+      <c r="U22" s="3">
         <v>25100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>59600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>21100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>22800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>23000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>25600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>28000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>25400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>25200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>24000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>24300</v>
       </c>
-      <c r="AI22" s="3" t="s">
+      <c r="AJ22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>318600</v>
+      </c>
+      <c r="E23" s="3">
         <v>266700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>187500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>248500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>244500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>267800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>253300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>276500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>347400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>400600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>340300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>280400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>333900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>274700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>219600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>165400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>185700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>91600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>190100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>172400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>239300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>256000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>249300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>264500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>274100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>245300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>186600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>224000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>216900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>208600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>179100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>168600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E24" s="3">
         <v>67800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>40600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>59300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>61300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>65100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>63200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>64900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>84900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>99100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>86100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>63900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>83200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>67400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>53100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>41800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>46600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>34900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>48400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>36200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>59500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>62400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>62500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>61900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>67400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>58700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>46500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>77200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>77800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>65400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>61700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>57900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>63700</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>238100</v>
+      </c>
+      <c r="E26" s="3">
         <v>198900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>146900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>189200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>183200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>202700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>190100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>211600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>262500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>301500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>254200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>216500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>250700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>207300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>166500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>123600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>139100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>56700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>141700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>136200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>179800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>193600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>186800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>202600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>206700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>186600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>140100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>146800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>139100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>143200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>117400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>110700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>236400</v>
+      </c>
+      <c r="E27" s="3">
         <v>197500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>145900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>187800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>181800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>200800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>188500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>210100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>260600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>298900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>252200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>215000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>249000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>205500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>165200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>122700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>138100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>56200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>140500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>135200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>178500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>192100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>185400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>201000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>205100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>185200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>139000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>144600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>138000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>142000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>116400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>109700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2778,8 +2839,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2796,11 +2857,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>2000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2808,11 +2869,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>122100</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,31 +3095,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-3600</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>-3600</v>
@@ -3064,19 +3134,19 @@
         <v>-3600</v>
       </c>
       <c r="N32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="O32" s="3">
         <v>-4900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-5000</v>
       </c>
       <c r="P32" s="3">
         <v>-5000</v>
       </c>
       <c r="Q32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="R32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-600</v>
       </c>
       <c r="S32" s="3">
         <v>-600</v>
@@ -3088,19 +3158,19 @@
         <v>-600</v>
       </c>
       <c r="V32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W32" s="3">
         <v>3100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3200</v>
-      </c>
-      <c r="X32" s="3">
-        <v>3300</v>
       </c>
       <c r="Y32" s="3">
         <v>3300</v>
       </c>
       <c r="Z32" s="3">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="AA32" s="3">
         <v>1300</v>
@@ -3109,11 +3179,11 @@
         <v>1300</v>
       </c>
       <c r="AC32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD32" s="3">
         <v>700</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
@@ -3127,111 +3197,117 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>197500</v>
+        <v>238100</v>
       </c>
       <c r="E33" s="3">
-        <v>145900</v>
+        <v>198900</v>
       </c>
       <c r="F33" s="3">
-        <v>187800</v>
+        <v>146900</v>
       </c>
       <c r="G33" s="3">
-        <v>181800</v>
+        <v>189200</v>
       </c>
       <c r="H33" s="3">
-        <v>200800</v>
+        <v>183200</v>
       </c>
       <c r="I33" s="3">
-        <v>188500</v>
+        <v>202700</v>
       </c>
       <c r="J33" s="3">
+        <v>190100</v>
+      </c>
+      <c r="K33" s="3">
         <v>210100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>260600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>298900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>252200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>215000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>249000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>205500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>165200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>122700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>138100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>56200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>140500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>135200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>178500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>192100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>185400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>203000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>205100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>185200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>139000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>266700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>138000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>142000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>116400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>109700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>197500</v>
+        <v>238100</v>
       </c>
       <c r="E35" s="3">
-        <v>145900</v>
+        <v>198900</v>
       </c>
       <c r="F35" s="3">
-        <v>187800</v>
+        <v>146900</v>
       </c>
       <c r="G35" s="3">
-        <v>181800</v>
+        <v>189200</v>
       </c>
       <c r="H35" s="3">
-        <v>200800</v>
+        <v>183200</v>
       </c>
       <c r="I35" s="3">
-        <v>188500</v>
+        <v>202700</v>
       </c>
       <c r="J35" s="3">
+        <v>190100</v>
+      </c>
+      <c r="K35" s="3">
         <v>210100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>260600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>298900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>252200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>215000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>249000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>205500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>165200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>122700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>138100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>56200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>140500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>135200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>178500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>192100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>185400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>203000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>205100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>185200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>139000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>266700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>138000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>142000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>116400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>109700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,171 +3698,175 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>676600</v>
+      </c>
+      <c r="E41" s="3">
         <v>613600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>692400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>648000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>573200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>477100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>367700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>320000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>648700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>667300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>628600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>618700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1702900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>972200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>983400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>974600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>949100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>853300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>764000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>679500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>738300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>569400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>442400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>361500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>293800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>199600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>102400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>216900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>370500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>321000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>254000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>239300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>279800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E42" s="3">
         <v>490800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>492300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>493500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>104000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>101900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>95600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>85200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>77700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>82300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>81300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>86100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>88300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>101700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>102500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>105600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>101200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>86900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>92300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>87900</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>8</v>
@@ -3790,8 +3880,8 @@
       <c r="AA42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -3814,474 +3904,489 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1216100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1145500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1045100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1037500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1045200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1023900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1031400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1067500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1118900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1212000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1140700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1078400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1078100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>981400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>908600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>837500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>864600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>823400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>879500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>872100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>941800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>958400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>930300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>918600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>991300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>936700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>908800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>900200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>851300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>755200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>733300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>703100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>731500</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1061900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1029500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1003600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1013100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>986100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>992200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1003400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>977300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>994900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>954200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>941200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>902500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>880100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>827200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>799600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>787900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>777600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>834500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>809900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>794100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>806300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>815700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>831700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>795600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>780600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>763700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>766400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>762500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>736600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>734400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>744500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>723600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>204500</v>
+        <v>127700</v>
       </c>
       <c r="E45" s="3">
-        <v>211700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>62300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>64800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>75500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>87300</v>
-      </c>
-      <c r="J45" s="3">
+        <v>125700</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>58300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>67300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>74600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>77600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>47000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>55400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>78600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>62800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>44700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>51200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>60900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>67900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>44800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>44900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>59200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>58000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>39400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>49000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>56600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>55000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>35500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>43400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>52800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>47300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>30300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>45100</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3241400</v>
+      </c>
+      <c r="E46" s="3">
         <v>3483900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3445100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3254400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2773300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2670600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2585400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2508300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2907500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2990400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2869400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2732700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3804800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2961100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2856900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2750300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2743700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2659000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2613600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2478400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2531300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2402700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2262400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2115100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2114700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1956600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1832600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1915100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2001800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1863400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1779100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1696300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1747000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E47" s="3">
         <v>68400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>68500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>64100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>49300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>50600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>56900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>64900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>67100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>61200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>68500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>60000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>57800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>49900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>47000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>42700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>45200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>36300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>57100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>58100</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>8</v>
@@ -4295,8 +4400,8 @@
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -4319,210 +4424,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4242600</v>
+      </c>
+      <c r="E48" s="3">
         <v>4228300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4133900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4143400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4142400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4172900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4185200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4198300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4100000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4036700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3935100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3767300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3591200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3473500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3444000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3427600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3362600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3344400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3373900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3386000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3342700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3345200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3327100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3108600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3065100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3026500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2961400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2924900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2881600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2872500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2887200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2895700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2878700</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1123700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1133100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1142500</v>
       </c>
-      <c r="F49" s="3">
-        <v>1152000</v>
-      </c>
       <c r="G49" s="3">
+        <v>1153900</v>
+      </c>
+      <c r="H49" s="3">
         <v>1161600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1171100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1180700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1190300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1199800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1209800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1221300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1231900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1131200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1140500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1149800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1159400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1168900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1178400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1247900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1257500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1267200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1276900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1286000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1295500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1262600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1272800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1282800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1293200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1079900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1087300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1095900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1105000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1046900</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E52" s="3">
         <v>68400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>67000</v>
       </c>
-      <c r="F52" s="3">
-        <v>67200</v>
-      </c>
       <c r="G52" s="3">
+        <v>42600</v>
+      </c>
+      <c r="H52" s="3">
         <v>51000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>41300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>40800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>42000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>70000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>43500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>44900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>45800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>48600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>51300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>53200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>52200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>53900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>55100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>55800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>49900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>49600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>53100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>50500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>57600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>59700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>63000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>64300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>63900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>80000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>81200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>80000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8753800</v>
+      </c>
+      <c r="E54" s="3">
         <v>8982100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8857000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8681100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8177600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8106500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8049000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8003800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8344400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8340600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8137800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7836800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8630800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7673600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7549000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7433200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7372600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7272000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7347600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7235800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7191100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7074400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6928600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6569700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6500000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6315600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6139800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6197500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6027200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5903200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5843400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5777000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5747200</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,135 +5230,139 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>459900</v>
+      </c>
+      <c r="E57" s="3">
         <v>474500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>449600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>402400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>405900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>365800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>410500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>410400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>485300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>528200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>546700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>452400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>499100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>405300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>402500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>387000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>352100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>315200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>389000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>351900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>385500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>382800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>405100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>382200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>438900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>431700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>427300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>402900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>379500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>349200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>367300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>323800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>402000</v>
+        <v>83800</v>
       </c>
       <c r="E58" s="3">
-        <v>401800</v>
+        <v>482300</v>
       </c>
       <c r="F58" s="3">
-        <v>401600</v>
+        <v>481000</v>
       </c>
       <c r="G58" s="3">
-        <v>401500</v>
+        <v>480200</v>
       </c>
       <c r="H58" s="3">
+        <v>478600</v>
+      </c>
+      <c r="I58" s="3">
+        <v>76900</v>
+      </c>
+      <c r="J58" s="3">
+        <v>74600</v>
+      </c>
+      <c r="K58" s="3">
         <v>1900</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1800</v>
       </c>
       <c r="L58" s="3">
         <v>1800</v>
@@ -5237,19 +5371,19 @@
         <v>1800</v>
       </c>
       <c r="N58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O58" s="3">
         <v>1700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>699800</v>
-      </c>
-      <c r="P58" s="3">
-        <v>1700</v>
       </c>
       <c r="Q58" s="3">
         <v>1700</v>
       </c>
       <c r="R58" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="S58" s="3">
         <v>1600</v>
@@ -5261,7 +5395,7 @@
         <v>1600</v>
       </c>
       <c r="V58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="W58" s="3">
         <v>1500</v>
@@ -5273,7 +5407,7 @@
         <v>1500</v>
       </c>
       <c r="Z58" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="AA58" s="3">
         <v>1400</v>
@@ -5285,10 +5419,10 @@
         <v>1400</v>
       </c>
       <c r="AD58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AE58" s="3">
         <v>151300</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>157800</v>
       </c>
       <c r="AF58" s="3">
         <v>157800</v>
@@ -5297,247 +5431,256 @@
         <v>157800</v>
       </c>
       <c r="AH58" s="3">
+        <v>157800</v>
+      </c>
+      <c r="AI58" s="3">
         <v>27100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>555000</v>
+        <v>258700</v>
       </c>
       <c r="E59" s="3">
-        <v>548900</v>
+        <v>241100</v>
       </c>
       <c r="F59" s="3">
-        <v>461700</v>
+        <v>256100</v>
       </c>
       <c r="G59" s="3">
-        <v>471500</v>
+        <v>115900</v>
       </c>
       <c r="H59" s="3">
-        <v>430000</v>
+        <v>123800</v>
       </c>
       <c r="I59" s="3">
-        <v>416500</v>
+        <v>123400</v>
       </c>
       <c r="J59" s="3">
+        <v>133600</v>
+      </c>
+      <c r="K59" s="3">
         <v>463200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>476300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>442900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>419400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>430700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>445500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>409800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>401600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>394000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>421700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>366800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>354000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>370400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>383700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>345300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>334100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>310000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>326200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>282700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>244900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>278500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>287000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>253200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>250900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>274500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1100500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1431500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1400300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1265700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1278900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>797700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>828900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>875500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>963400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>972900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>967900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>884800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1644400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>816800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>805800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>782600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>775400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>683600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>744600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>723800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>770700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>729600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>740700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>693600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>766500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>715800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>673600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>832700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>824300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>760200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>776000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>625400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2480900</v>
+        <v>2670300</v>
       </c>
       <c r="E61" s="3">
-        <v>2481000</v>
+        <v>2678000</v>
       </c>
       <c r="F61" s="3">
-        <v>2480900</v>
+        <v>2681700</v>
       </c>
       <c r="G61" s="3">
-        <v>2085000</v>
+        <v>2693000</v>
       </c>
       <c r="H61" s="3">
-        <v>2484500</v>
+        <v>2298000</v>
       </c>
       <c r="I61" s="3">
-        <v>2484400</v>
+        <v>2706400</v>
       </c>
       <c r="J61" s="3">
-        <v>2484400</v>
+        <v>2709500</v>
       </c>
       <c r="K61" s="3">
         <v>2484400</v>
       </c>
       <c r="L61" s="3">
+        <v>2484400</v>
+      </c>
+      <c r="M61" s="3">
         <v>2484300</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2484200</v>
       </c>
       <c r="N61" s="3">
         <v>2484200</v>
@@ -5546,168 +5689,174 @@
         <v>2484200</v>
       </c>
       <c r="P61" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="Q61" s="3">
         <v>2493300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2494000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2493800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2493500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2493200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2493000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2492800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2502700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2502200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2501800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2501300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2500800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2500400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2499800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2499400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2475600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2477000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2478400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2640300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2646500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>943100</v>
+        <v>178900</v>
       </c>
       <c r="E62" s="3">
-        <v>944700</v>
+        <v>193900</v>
       </c>
       <c r="F62" s="3">
-        <v>937200</v>
+        <v>177500</v>
       </c>
       <c r="G62" s="3">
-        <v>926500</v>
+        <v>91800</v>
       </c>
       <c r="H62" s="3">
-        <v>975700</v>
+        <v>176700</v>
       </c>
       <c r="I62" s="3">
-        <v>978000</v>
+        <v>215200</v>
       </c>
       <c r="J62" s="3">
+        <v>206700</v>
+      </c>
+      <c r="K62" s="3">
         <v>976800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>925400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>918900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>906400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>860600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>893900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>919200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>918000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>910500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>898300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>962100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>960100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>948200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>883000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>921400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>891500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>702400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>702500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>711400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>692600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>682800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>733100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>759400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>764300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>751500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>733200</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4490200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4855500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4826000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4683800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4290400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4257900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4291300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4336700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4373200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4376100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4358500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4229600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5022500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4229300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4217800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4186900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4167200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4138900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4197700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4164800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4156400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4153200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4134000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3897300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3969800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3927600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3866000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4014900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4033000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3996600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4018700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4017200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4017600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3669100</v>
+      </c>
+      <c r="E72" s="3">
         <v>3544400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3459600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3447200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3370500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3339000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3259300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3186800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3443500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3437000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3261900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3102100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3162800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3008500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2906300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2835500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2806700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2742900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2771100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2704800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2643700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2539200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2427800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2315800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2185500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2054000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1949600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1867400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1658200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1578800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1504500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1447100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1396900</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4263600</v>
+      </c>
+      <c r="E76" s="3">
         <v>4126600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4031000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3997300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3887200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3848600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3757700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3667100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3971200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3964500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3779300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3607200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3608300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3444300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3331200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3246300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3205400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3133100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3149900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3071000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3034700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2921200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2794600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2672400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2530200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2388000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2273800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2182600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1994200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1906600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1824700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1759800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1729600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>197500</v>
+        <v>238100</v>
       </c>
       <c r="E81" s="3">
-        <v>145900</v>
+        <v>198900</v>
       </c>
       <c r="F81" s="3">
-        <v>187800</v>
+        <v>146900</v>
       </c>
       <c r="G81" s="3">
-        <v>181800</v>
+        <v>189200</v>
       </c>
       <c r="H81" s="3">
-        <v>200800</v>
+        <v>183200</v>
       </c>
       <c r="I81" s="3">
-        <v>188500</v>
+        <v>202700</v>
       </c>
       <c r="J81" s="3">
+        <v>190100</v>
+      </c>
+      <c r="K81" s="3">
         <v>210100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>260600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>298900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>252200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>215000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>249000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>205500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>165200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>122700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>138100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>56200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>140500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>135200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>178500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>192100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>185400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>203000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>205100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>185200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>139000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>266700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>138000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>142000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>116400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>109700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>128500</v>
+        <v>117300</v>
       </c>
       <c r="E83" s="3">
-        <v>128400</v>
+        <v>115300</v>
       </c>
       <c r="F83" s="3">
-        <v>130900</v>
+        <v>113600</v>
       </c>
       <c r="G83" s="3">
-        <v>129400</v>
+        <v>102800</v>
       </c>
       <c r="H83" s="3">
-        <v>127900</v>
+        <v>102700</v>
       </c>
       <c r="I83" s="3">
-        <v>129500</v>
+        <v>104100</v>
       </c>
       <c r="J83" s="3">
+        <v>98400</v>
+      </c>
+      <c r="K83" s="3">
         <v>118800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>114000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>114300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>109700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>106400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>105600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>104700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>100900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>100500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>108200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>100300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>98900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>97900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>95900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>94800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>97300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>101400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>104100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>108100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>107700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>97500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>93700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>92500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>93700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>327100</v>
+      </c>
+      <c r="E89" s="3">
         <v>278300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>260400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>335300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>339500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>359900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>280400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>420100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>430600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>319000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>325300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>390700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>283600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>228200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>191600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>271100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>298200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>226800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>236700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>329200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>339800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>302400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>236000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>345600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>301000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>331000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>202500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>272800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>197700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>221500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>164100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>213400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>217300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-245300</v>
+        <v>-146700</v>
       </c>
       <c r="E91" s="3">
-        <v>-78100</v>
+        <v>-245000</v>
       </c>
       <c r="F91" s="3">
-        <v>-141200</v>
+        <v>-76700</v>
       </c>
       <c r="G91" s="3">
-        <v>-90100</v>
+        <v>-141100</v>
       </c>
       <c r="H91" s="3">
-        <v>-127000</v>
+        <v>-89800</v>
       </c>
       <c r="I91" s="3">
-        <v>-114000</v>
+        <v>-126400</v>
       </c>
       <c r="J91" s="3">
+        <v>-112400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-247500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-182800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-184500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-215600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-238900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-149900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-60700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-174400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-139000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>249300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-242800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-81000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-544000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-88900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-126800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-115400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-251800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-183800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-176900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-221200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-429400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-144800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-132700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-87500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-170200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-127100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-51800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-77000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-278300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-95500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-92700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-80100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-202900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-131800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-166300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-381500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-86700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-83100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-57800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-186900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-455000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,43 +8819,44 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-112200</v>
+        <v>112300</v>
       </c>
       <c r="E96" s="3">
-        <v>-112000</v>
+        <v>112200</v>
       </c>
       <c r="F96" s="3">
-        <v>-112000</v>
+        <v>112000</v>
       </c>
       <c r="G96" s="3">
-        <v>-112400</v>
+        <v>112000</v>
       </c>
       <c r="H96" s="3">
-        <v>-112400</v>
+        <v>112400</v>
       </c>
       <c r="I96" s="3">
-        <v>-112100</v>
+        <v>112400</v>
       </c>
       <c r="J96" s="3">
+        <v>112100</v>
+      </c>
+      <c r="K96" s="3">
         <v>-115900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-117200</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-93600</v>
       </c>
       <c r="M96" s="3">
         <v>-93600</v>
       </c>
       <c r="N96" s="3">
-        <v>-95000</v>
+        <v>-93600</v>
       </c>
       <c r="O96" s="3">
         <v>-95000</v>
@@ -8631,43 +8865,43 @@
         <v>-95000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-94800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-75000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-74900</v>
       </c>
       <c r="T96" s="3">
         <v>-74900</v>
       </c>
       <c r="U96" s="3">
-        <v>-74800</v>
+        <v>-74900</v>
       </c>
       <c r="V96" s="3">
         <v>-74800</v>
       </c>
       <c r="W96" s="3">
-        <v>-74600</v>
+        <v>-74800</v>
       </c>
       <c r="X96" s="3">
         <v>-74600</v>
       </c>
       <c r="Y96" s="3">
-        <v>-74700</v>
+        <v>-74600</v>
       </c>
       <c r="Z96" s="3">
         <v>-74700</v>
       </c>
       <c r="AA96" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-74500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-59500</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-59400</v>
       </c>
       <c r="AD96" s="3">
         <v>-59400</v>
@@ -8685,10 +8919,13 @@
         <v>-59400</v>
       </c>
       <c r="AI96" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,76 +9233,79 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-513400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-114300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-135000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>283500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-154500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-123700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-117300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-497000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-265400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-103400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-94200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1045500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>591900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-106700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-95300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-75400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-75300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-85700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-75200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-109700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-75400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-82700</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>-75000</v>
       </c>
       <c r="Z100" s="3">
         <v>-75000</v>
@@ -9068,54 +9314,57 @@
         <v>-75000</v>
       </c>
       <c r="AB100" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-67500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-209800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-44900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-91600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-78800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>44400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>74800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>96100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>109400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>47700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-328700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>38700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1084200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>730700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>25500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>95800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>89300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>84500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-58800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>168900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>127000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>80900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>67700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>94200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>97200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-114500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-153600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>49500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>67000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>14700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-40500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>66200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>PKG</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2146100</v>
+      </c>
+      <c r="E8" s="3">
         <v>2182400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2075300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1979500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1937900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1936000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1952100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1976300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1978400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2125900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2237300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2136400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2043200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2000100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1879900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1807200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1714200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1693700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1541600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1708700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1720000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1750700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1759900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1733700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1746500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1809900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1767500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1690600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1684300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1640100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1584000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1536500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1476600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1484000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1675400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1677200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1637600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1607100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1524800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1520300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1504400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1538900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1528100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1607500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1648500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1603200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1533300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1489400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1431100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1403500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1380900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1348300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1209700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1342900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1336700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1339300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1332000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1312300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1321100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1366700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1346900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1334500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1312600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1242800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1219400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1198000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1149500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1154500</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>470700</v>
+      </c>
+      <c r="E10" s="3">
         <v>505200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>437700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>372400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>413100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>415700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>447700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>437400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>450300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>518400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>588800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>533200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>509900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>510700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>448800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>403700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>333300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>345400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>331900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>365800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>383300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>411400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>427900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>421400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>425400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>443200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>420600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>356100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>371700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>397300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>364600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>338500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>327100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>329500</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,139 +1377,145 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E14" s="3">
         <v>11700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>17600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>13700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>17000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>58000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-3100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>74600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>7200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>21500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>3500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E15" s="3">
         <v>132500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>128500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>126900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>124500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>126800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>124900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>123200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1828300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1842400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1790700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1764800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1664600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1667300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1655900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1690600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1690400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1765600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1821500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1779900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1745900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1647800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1585300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1568900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1525000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1484200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1425500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1499600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1484900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1487900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1479500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1458300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1459800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1511400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1497900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1477700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1432300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1397800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1350200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1333400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1283700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1277600</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>317800</v>
+      </c>
+      <c r="E18" s="3">
         <v>340000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>284600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>214700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>273300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>268700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>296200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>285700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>288000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>360300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>415800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>356500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>297300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>352300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>294600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>238300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>189200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>209500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>116100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>209100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>235100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>262800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>280400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>275400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>286700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>298500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>269600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>212900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>252000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>242300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>233800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>203100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>192900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>206400</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,8 +1909,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>3600</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>3600</v>
@@ -1889,19 +1922,19 @@
         <v>3600</v>
       </c>
       <c r="O20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="P20" s="3">
         <v>4900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>5000</v>
       </c>
       <c r="Q20" s="3">
         <v>5000</v>
       </c>
       <c r="R20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="S20" s="3">
         <v>4800</v>
-      </c>
-      <c r="S20" s="3">
-        <v>600</v>
       </c>
       <c r="T20" s="3">
         <v>600</v>
@@ -1913,19 +1946,19 @@
         <v>600</v>
       </c>
       <c r="W20" s="3">
+        <v>600</v>
+      </c>
+      <c r="X20" s="3">
         <v>-3100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3200</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-3300</v>
       </c>
       <c r="Z20" s="3">
         <v>-3300</v>
       </c>
       <c r="AA20" s="3">
-        <v>-1300</v>
+        <v>-3300</v>
       </c>
       <c r="AB20" s="3">
         <v>-1300</v>
@@ -1934,11 +1967,11 @@
         <v>-1300</v>
       </c>
       <c r="AD20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-700</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
@@ -1952,426 +1985,441 @@
         <v>0</v>
       </c>
       <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-23400</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>450800</v>
+      </c>
+      <c r="E21" s="3">
         <v>472500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>413100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>341600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>397800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>395500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>421100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>408900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>410400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>477900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>533700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>469800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>408600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>462900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>404300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>343900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>290700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>310600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>224900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>310000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>330900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>357500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>373000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>366900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>382700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>398600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>372400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>320300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>359700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>339800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>327500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>295600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>286600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E22" s="3">
         <v>9700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>15400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>24900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>23500</v>
-      </c>
-      <c r="S22" s="3">
-        <v>24400</v>
       </c>
       <c r="T22" s="3">
         <v>24400</v>
       </c>
       <c r="U22" s="3">
+        <v>24400</v>
+      </c>
+      <c r="V22" s="3">
         <v>25100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>19600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>59600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>21100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>22800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>20900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>23100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>23000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>25600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>28000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>25400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>25200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>24000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>24300</v>
       </c>
-      <c r="AJ22" s="3" t="s">
+      <c r="AK22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>291600</v>
+      </c>
+      <c r="E23" s="3">
         <v>318600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>266700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>187500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>248500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>244500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>267800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>253300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>276500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>347400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>400600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>340300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>280400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>333900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>274700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>219600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>165400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>185700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>91600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>190100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>172400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>239300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>256000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>249300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>264500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>274100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>245300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>186600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>224000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>216900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>208600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>179100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>168600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E24" s="3">
         <v>80500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>67800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>40600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>59300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>65100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>63200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>64900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>84900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>99100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>86100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>63900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>83200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>67400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>53100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>41800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>46600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>34900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>48400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>36200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>59500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>62400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>62500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>61900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>67400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>58700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>46500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>77200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>77800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>65400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>61700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>57900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>63700</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>221100</v>
+      </c>
+      <c r="E26" s="3">
         <v>238100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>198900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>146900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>189200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>183200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>202700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>190100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>211600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>262500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>301500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>254200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>216500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>250700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>207300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>166500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>123600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>139100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>56700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>141700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>136200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>179800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>193600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>186800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>202600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>206700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>186600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>140100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>146800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>139100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>143200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>117400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>110700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>219600</v>
+      </c>
+      <c r="E27" s="3">
         <v>236400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>197500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>145900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>187800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>181800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>200800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>188500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>210100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>260600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>298900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>252200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>215000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>249000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>205500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>165200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>122700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>138100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>56200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>140500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>135200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>178500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>192100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>185400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>201000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>205100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>185200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>139000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>144600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>138000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>142000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>116400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>109700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2842,8 +2902,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2860,11 +2920,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>2000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2872,11 +2932,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>122100</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,8 +3193,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>-3600</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>-3600</v>
@@ -3137,19 +3206,19 @@
         <v>-3600</v>
       </c>
       <c r="O32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="P32" s="3">
         <v>-4900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-5000</v>
       </c>
       <c r="Q32" s="3">
         <v>-5000</v>
       </c>
       <c r="R32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="S32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-600</v>
       </c>
       <c r="T32" s="3">
         <v>-600</v>
@@ -3161,19 +3230,19 @@
         <v>-600</v>
       </c>
       <c r="W32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X32" s="3">
         <v>3100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3200</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>3300</v>
       </c>
       <c r="Z32" s="3">
         <v>3300</v>
       </c>
       <c r="AA32" s="3">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="AB32" s="3">
         <v>1300</v>
@@ -3182,11 +3251,11 @@
         <v>1300</v>
       </c>
       <c r="AD32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE32" s="3">
         <v>700</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
@@ -3200,114 +3269,120 @@
         <v>0</v>
       </c>
       <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>221100</v>
+      </c>
+      <c r="E33" s="3">
         <v>238100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>198900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>146900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>189200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>183200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>202700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>190100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>210100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>260600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>298900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>252200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>215000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>249000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>205500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>165200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>122700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>138100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>56200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>140500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>135200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>178500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>192100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>185400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>203000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>205100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>185200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>139000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>266700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>138000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>142000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>116400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>109700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>221100</v>
+      </c>
+      <c r="E35" s="3">
         <v>238100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>198900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>146900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>189200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>183200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>202700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>190100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>210100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>260600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>298900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>252200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>215000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>249000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>205500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>165200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>122700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>138100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>56200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>140500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>135200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>178500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>192100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>185400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>203000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>205100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>185200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>139000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>266700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>138000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>142000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>116400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>109700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,177 +3784,181 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>685000</v>
+      </c>
+      <c r="E41" s="3">
         <v>676600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>613600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>692400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>648000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>573200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>477100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>367700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>320000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>648700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>667300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>628600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>618700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1702900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>972200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>983400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>974600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>949100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>853300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>764000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>679500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>738300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>569400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>442400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>361500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>293800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>199600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>102400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>216900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>370500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>321000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>254000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>239300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>279800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E42" s="3">
         <v>95000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>490800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>492300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>493500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>104000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>101900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>95600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>85200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>77700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>82300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>81300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>86100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>88300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>101700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>102500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>105600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>101200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>86900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>92300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>87900</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>8</v>
@@ -3883,8 +3972,8 @@
       <c r="AB42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3907,227 +3996,236 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1154200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1216100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1145500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1045100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1037500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1045200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1023900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1031400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1067500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1118900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1212000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1140700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1078400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1078100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>981400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>908600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>837500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>864600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>823400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>879500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>872100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>941800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>958400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>930300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>918600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>991300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>936700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>908800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>900200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>851300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>755200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>733300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>703100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>731500</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1124900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1061900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1029500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1003600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1013100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>986100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>992200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1003400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>977300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>994900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>954200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>941200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>902500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>880100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>827200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>799600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>787900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>777600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>834500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>809900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>794100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>806300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>815700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>831700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>795600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>780600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>763700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>766400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>762500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>736600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>734400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>744500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>723600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>127700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>125700</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
@@ -4141,255 +4239,261 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>58300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>67300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>74600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>77600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>47000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>55400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>78600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>62800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>44700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>51200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>60900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>67900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>44800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>44900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>59200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>58000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>39400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>49000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>56600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>55000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>35500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>43400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>52800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>47300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>30300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>45100</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3233000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3241400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3483900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3445100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3254400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2773300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2670600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2585400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2508300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2907500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2990400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2869400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2732700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3804800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2961100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2856900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2750300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2743700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2659000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2613600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2478400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2531300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2402700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2262400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2115100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2114700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1956600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1832600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1915100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2001800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1863400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1779100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1696300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1747000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E47" s="3">
         <v>69700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>68400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>68500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>64100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>49300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>50600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>56900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>64900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>67100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>61200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>68500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>60000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>57800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>49900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>47000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>42700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>45200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>36300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>57100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>58100</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>8</v>
@@ -4403,8 +4507,8 @@
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -4427,216 +4531,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4315900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4242600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4228300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4133900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4143400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4142400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4172900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4185200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4198300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4100000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4036700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3935100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3767300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3591200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3473500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3444000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3427600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3362600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3344400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3373900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3386000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3342700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3345200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3327100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3108600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3065100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3026500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2961400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2924900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2881600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2872500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2887200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2895700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2878700</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1115300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1123700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1133100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1142500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1153900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1161600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1171100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1180700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1190300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1199800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1209800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1221300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1231900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1131200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1140500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1149800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1159400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1168900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1178400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1247900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1257500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1267200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1276900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1286000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1295500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1262600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1272800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1282800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1293200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1079900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1087300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1095900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1105000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1046900</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E52" s="3">
         <v>76400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>68400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>67000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>51000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>41300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>40800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>42000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>70000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>43500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>44900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>45800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>48600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>51300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>53200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>52200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>53900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>55100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>55800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>49900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>49600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>53100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>50500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>57600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>59700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>63000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>64300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>63900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>80000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>81200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>80000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8833200</v>
+      </c>
+      <c r="E54" s="3">
         <v>8753800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8982100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8857000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8681100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8177600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8106500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8049000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8003800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8344400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8340600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8137800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7836800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8630800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7673600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7549000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7433200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7372600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7272000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7347600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7235800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7191100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7074400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6928600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6569700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6500000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6315600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6139800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6197500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6027200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5903200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5843400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5777000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5747200</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,141 +5360,145 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>430300</v>
+      </c>
+      <c r="E57" s="3">
         <v>459900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>474500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>449600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>402400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>405900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>365800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>410500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>410400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>485300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>528200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>546700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>452400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>499100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>405300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>402500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>387000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>352100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>315200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>389000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>351900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>385500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>382800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>405100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>382200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>438900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>431700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>427300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>402900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>379500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>349200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>367300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>323800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E58" s="3">
         <v>83800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>482300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>481000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>480200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>478600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>76900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>74600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1900</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1800</v>
       </c>
       <c r="M58" s="3">
         <v>1800</v>
@@ -5374,19 +5507,19 @@
         <v>1800</v>
       </c>
       <c r="O58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P58" s="3">
         <v>1700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>699800</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>1700</v>
       </c>
       <c r="R58" s="3">
         <v>1700</v>
       </c>
       <c r="S58" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="T58" s="3">
         <v>1600</v>
@@ -5398,7 +5531,7 @@
         <v>1600</v>
       </c>
       <c r="W58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="X58" s="3">
         <v>1500</v>
@@ -5410,7 +5543,7 @@
         <v>1500</v>
       </c>
       <c r="AA58" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="AB58" s="3">
         <v>1400</v>
@@ -5422,10 +5555,10 @@
         <v>1400</v>
       </c>
       <c r="AE58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AF58" s="3">
         <v>151300</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>157800</v>
       </c>
       <c r="AG58" s="3">
         <v>157800</v>
@@ -5434,256 +5567,265 @@
         <v>157800</v>
       </c>
       <c r="AI58" s="3">
+        <v>157800</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>27100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>212500</v>
+      </c>
+      <c r="E59" s="3">
         <v>258700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>241100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>256100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>115900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>123800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>123400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>133600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>463200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>476300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>442900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>419400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>430700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>445500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>409800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>401600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>394000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>421700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>366800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>354000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>370400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>383700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>345300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>334100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>310000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>326200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>282700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>244900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>278500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>287000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>253200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>250900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>274500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1001600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1100500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1431500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1400300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1265700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1278900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>797700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>828900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>875500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>963400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>972900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>967900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>884800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1644400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>816800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>805800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>782600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>775400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>683600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>744600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>723800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>770700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>729600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>740700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>693600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>766500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>715800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>673600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>832700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>824300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>760200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>776000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>625400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2688900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2670300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2678000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2681700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2693000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2298000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2706400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2709500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2484400</v>
       </c>
       <c r="L61" s="3">
         <v>2484400</v>
       </c>
       <c r="M61" s="3">
+        <v>2484400</v>
+      </c>
+      <c r="N61" s="3">
         <v>2484300</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2484200</v>
       </c>
       <c r="O61" s="3">
         <v>2484200</v>
@@ -5692,171 +5834,177 @@
         <v>2484200</v>
       </c>
       <c r="Q61" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="R61" s="3">
         <v>2493300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2494000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2493800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2493500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2493200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2493000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2492800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2502700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2502200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2501800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2501300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2500800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2500400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2499800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2499400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2475600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2477000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2478400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2640300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2646500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>121300</v>
+      </c>
+      <c r="E62" s="3">
         <v>178900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>193900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>177500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>91800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>176700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>215200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>206700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>976800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>925400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>918900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>906400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>860600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>893900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>919200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>918000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>910500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>898300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>962100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>960100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>948200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>883000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>921400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>891500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>702400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>702500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>711400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>692600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>682800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>733100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>759400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>764300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>751500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>733200</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4429200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4490200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4855500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4826000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4683800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4290400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4257900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4291300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4336700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4373200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4376100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4358500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4229600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5022500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4229300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4217800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4186900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4167200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4138900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4197700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4164800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4156400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4153200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4134000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3897300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3969800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3927600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3866000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4014900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4033000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3996600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4018700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4017200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4017600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3776700</v>
+      </c>
+      <c r="E72" s="3">
         <v>3669100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3544400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3459600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3447200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3370500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3339000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3259300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3186800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3443500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3437000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3261900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3102100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3162800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3008500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2906300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2835500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2806700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2742900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2771100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2704800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2643700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2539200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2427800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2315800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2185500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2054000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1949600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1867400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1658200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1578800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1504500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1447100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1396900</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4404000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4263600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4126600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4031000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3997300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3887200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3848600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3757700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3667100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3971200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3964500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3779300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3607200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3608300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3444300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3331200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3246300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3205400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3133100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3149900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3071000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3034700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2921200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2794600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2672400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2530200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2388000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2273800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2182600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1994200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1906600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1824700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1759800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1729600</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>221100</v>
+      </c>
+      <c r="E81" s="3">
         <v>238100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>198900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>146900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>189200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>183200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>202700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>190100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>210100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>260600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>298900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>252200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>215000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>249000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>205500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>165200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>122700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>138100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>56200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>140500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>135200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>178500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>192100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>185400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>203000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>205100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>185200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>139000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>266700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>138000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>142000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>116400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>109700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E83" s="3">
         <v>117300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>115300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>113600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>102800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>102700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>104100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>98400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>118800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>114000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>114300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>109700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>106400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>105600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>104700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>100800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>100900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>100500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>108200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>100300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>98900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>97900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>95900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>94800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>97300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>101400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>104100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>108100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>107700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>97500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>93700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>92500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>93700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>325400</v>
+      </c>
+      <c r="E89" s="3">
         <v>327100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>278300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>260400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>335300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>339500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>359900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>280400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>420100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>430600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>319000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>325300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>390700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>283600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>228200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>191600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>271100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>298200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>226800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>236700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>329200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>339800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>302400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>236000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>345600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>301000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>331000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>202500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>272800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>197700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>221500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>164100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>213400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>217300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-201300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-146700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-245000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-76700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-141100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-89800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-126400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-112400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-247500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-182800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-184500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-215600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-238900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-149900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-60700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-174400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-139000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-203300</v>
+      </c>
+      <c r="E94" s="3">
         <v>249300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-242800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-81000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-544000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-88900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-126800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-115400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-251800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-183800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-176900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-221200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-429400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-144800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-132700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-87500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-170200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-127100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-51800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-77000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-278300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-95500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-92700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-80100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-202900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-131800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-166300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-381500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-86700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-83100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-57800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-186900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-455000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8829,37 +9062,37 @@
         <v>112300</v>
       </c>
       <c r="E96" s="3">
+        <v>112300</v>
+      </c>
+      <c r="F96" s="3">
         <v>112200</v>
-      </c>
-      <c r="F96" s="3">
-        <v>112000</v>
       </c>
       <c r="G96" s="3">
         <v>112000</v>
       </c>
       <c r="H96" s="3">
-        <v>112400</v>
+        <v>112000</v>
       </c>
       <c r="I96" s="3">
         <v>112400</v>
       </c>
       <c r="J96" s="3">
+        <v>112400</v>
+      </c>
+      <c r="K96" s="3">
         <v>112100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-115900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-117200</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-93600</v>
       </c>
       <c r="N96" s="3">
         <v>-93600</v>
       </c>
       <c r="O96" s="3">
-        <v>-95000</v>
+        <v>-93600</v>
       </c>
       <c r="P96" s="3">
         <v>-95000</v>
@@ -8868,43 +9101,43 @@
         <v>-95000</v>
       </c>
       <c r="R96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-94800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-75000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-74900</v>
       </c>
       <c r="U96" s="3">
         <v>-74900</v>
       </c>
       <c r="V96" s="3">
-        <v>-74800</v>
+        <v>-74900</v>
       </c>
       <c r="W96" s="3">
         <v>-74800</v>
       </c>
       <c r="X96" s="3">
-        <v>-74600</v>
+        <v>-74800</v>
       </c>
       <c r="Y96" s="3">
         <v>-74600</v>
       </c>
       <c r="Z96" s="3">
-        <v>-74700</v>
+        <v>-74600</v>
       </c>
       <c r="AA96" s="3">
         <v>-74700</v>
       </c>
       <c r="AB96" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-74500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-59500</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-59400</v>
       </c>
       <c r="AE96" s="3">
         <v>-59400</v>
@@ -8922,10 +9155,13 @@
         <v>-59400</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,79 +9478,82 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-113700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-513400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-114300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-135000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>283500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-154500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-123700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-117300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-497000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-265400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-103400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-94200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1045500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>591900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-106700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-95300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-75400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-75300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-85700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-75200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-109700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-75400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-82700</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>-75000</v>
       </c>
       <c r="AA100" s="3">
         <v>-75000</v>
@@ -9317,31 +9562,34 @@
         <v>-75000</v>
       </c>
       <c r="AC100" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-67500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-209800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-44900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-91600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,108 +9692,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E102" s="3">
         <v>63000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-78800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>44400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>74800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>96100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>109400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>47700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-328700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>38700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1084200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>730700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>25500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>95800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>89300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>84500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-58800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>168900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>127000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>80900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>67700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>94200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>97200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-114500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-153600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>49500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>67000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>14700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-40500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>66200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>PKG</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2141000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2146100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2182400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2075300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1979500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1937900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1936000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1952100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1976300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1978400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2125900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2237300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2136400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2043200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2000100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1879900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1807200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1714200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1693700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1541600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1708700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1720000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1750700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1759900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1733700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1746500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1809900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1767500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1690600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1684300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1640100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1584000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1536500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1476600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1484000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1682300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1675400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1677200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1637600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1607100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1524800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1520300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1504400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1538900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1528100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1607500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1648500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1603200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1533300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1489400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1431100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1403500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1380900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1348300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1209700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1342900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1336700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1339300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1332000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1312300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1321100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1366700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1346900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1334500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1312600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1242800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1219400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1198000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1149500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1154500</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>458700</v>
+      </c>
+      <c r="E10" s="3">
         <v>470700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>505200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>437700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>372400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>413100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>415700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>447700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>437400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>450300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>518400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>588800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>533200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>509900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>510700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>448800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>403700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>333300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>345400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>331900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>365800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>383300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>411400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>427900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>421400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>425400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>443200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>420600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>356100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>371700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>397300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>364600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>338500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>327100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>329500</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1389,136 +1409,139 @@
         <v>14500</v>
       </c>
       <c r="E14" s="3">
+        <v>14500</v>
+      </c>
+      <c r="F14" s="3">
         <v>11700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>17600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>13700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>17000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>58000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-3100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>74600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>7200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>21500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>6000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E15" s="3">
         <v>133000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>132500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>128500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>126900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>124500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>126800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>124900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>123200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1846200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1828300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1842400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1790700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1764800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1664600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1667300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1655900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1690600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1690400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1765600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1821500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1779900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1745900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1647800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1585300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1568900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1525000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1484200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1425500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1499600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1484900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1487900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1479500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1458300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1459800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1511400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1497900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1477700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1432300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1397800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1350200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1333400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1283700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1277600</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>294800</v>
+      </c>
+      <c r="E18" s="3">
         <v>317800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>340000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>284600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>214700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>273300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>268700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>296200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>285700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>288000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>360300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>415800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>356500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>297300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>352300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>294600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>238300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>189200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>209500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>116100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>209100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>235100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>262800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>280400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>275400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>286700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>298500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>269600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>212900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>252000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>242300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>233800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>203100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>192900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>206400</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1912,8 +1946,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>3600</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>3600</v>
@@ -1925,19 +1959,19 @@
         <v>3600</v>
       </c>
       <c r="P20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q20" s="3">
         <v>4900</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>5000</v>
       </c>
       <c r="R20" s="3">
         <v>5000</v>
       </c>
       <c r="S20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="T20" s="3">
         <v>4800</v>
-      </c>
-      <c r="T20" s="3">
-        <v>600</v>
       </c>
       <c r="U20" s="3">
         <v>600</v>
@@ -1949,19 +1983,19 @@
         <v>600</v>
       </c>
       <c r="X20" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-3300</v>
       </c>
       <c r="AA20" s="3">
         <v>-3300</v>
       </c>
       <c r="AB20" s="3">
-        <v>-1300</v>
+        <v>-3300</v>
       </c>
       <c r="AC20" s="3">
         <v>-1300</v>
@@ -1970,11 +2004,11 @@
         <v>-1300</v>
       </c>
       <c r="AE20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-700</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
@@ -1988,438 +2022,453 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-23400</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>429700</v>
+      </c>
+      <c r="E21" s="3">
         <v>450800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>472500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>413100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>341600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>397800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>395500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>421100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>408900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>410400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>477900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>533700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>469800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>408600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>462900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>404300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>343900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>290700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>310600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>224900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>310000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>330900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>357500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>373000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>366900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>382700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>398600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>372400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>320300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>359700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>339800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>327500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>295600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>286600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E22" s="3">
         <v>9900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>23400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>24900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>23500</v>
-      </c>
-      <c r="T22" s="3">
-        <v>24400</v>
       </c>
       <c r="U22" s="3">
         <v>24400</v>
       </c>
       <c r="V22" s="3">
+        <v>24400</v>
+      </c>
+      <c r="W22" s="3">
         <v>25100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>59600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>21100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>22800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>23100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>23000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>25600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>28000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>25400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>25200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>24000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>24300</v>
       </c>
-      <c r="AK22" s="3" t="s">
+      <c r="AL22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>267400</v>
+      </c>
+      <c r="E23" s="3">
         <v>291600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>318600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>266700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>187500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>248500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>244500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>267800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>253300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>276500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>347400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>400600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>340300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>280400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>333900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>274700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>219600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>165400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>185700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>91600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>190100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>172400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>239300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>256000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>249300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>264500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>274100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>245300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>186600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>224000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>216900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>208600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>179100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>168600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>63600</v>
+      </c>
+      <c r="E24" s="3">
         <v>70500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>80500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>67800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>40600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>59300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>61300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>65100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>63200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>64900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>84900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>99100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>86100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>63900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>83200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>67400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>53100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>41800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>46600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>34900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>48400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>36200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>59500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>62400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>62500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>61900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>67400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>58700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>46500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>77200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>77800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>65400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>61700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>57900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>63700</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>203800</v>
+      </c>
+      <c r="E26" s="3">
         <v>221100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>238100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>198900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>146900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>189200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>183200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>202700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>190100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>211600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>262500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>301500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>254200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>216500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>250700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>207300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>166500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>123600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>139100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>56700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>141700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>136200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>179800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>193600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>186800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>202600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>206700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>186600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>140100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>146800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>139100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>143200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>117400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>110700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>202400</v>
+      </c>
+      <c r="E27" s="3">
         <v>219600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>236400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>197500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>145900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>187800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>181800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>200800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>188500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>210100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>260600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>298900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>252200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>215000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>249000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>205500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>165200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>122700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>138100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>56200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>140500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>135200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>178500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>192100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>185400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>201000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>205100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>185200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>139000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>144600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>138000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>142000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>116400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>109700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2905,8 +2966,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2923,11 +2984,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>2000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2935,11 +2996,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>122100</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3196,8 +3266,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>-3600</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>-3600</v>
@@ -3209,19 +3279,19 @@
         <v>-3600</v>
       </c>
       <c r="P32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-4900</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-5000</v>
       </c>
       <c r="R32" s="3">
         <v>-5000</v>
       </c>
       <c r="S32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="T32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-600</v>
       </c>
       <c r="U32" s="3">
         <v>-600</v>
@@ -3233,19 +3303,19 @@
         <v>-600</v>
       </c>
       <c r="X32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y32" s="3">
         <v>3100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>3300</v>
       </c>
       <c r="AA32" s="3">
         <v>3300</v>
       </c>
       <c r="AB32" s="3">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="AC32" s="3">
         <v>1300</v>
@@ -3254,11 +3324,11 @@
         <v>1300</v>
       </c>
       <c r="AE32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AF32" s="3">
         <v>700</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
@@ -3272,117 +3342,123 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>203800</v>
+      </c>
+      <c r="E33" s="3">
         <v>221100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>238100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>198900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>146900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>189200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>183200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>202700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>190100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>210100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>260600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>298900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>252200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>215000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>249000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>205500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>165200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>122700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>138100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>56200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>140500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>135200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>178500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>192100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>185400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>203000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>205100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>185200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>139000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>266700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>138000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>142000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>116400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>109700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>203800</v>
+      </c>
+      <c r="E35" s="3">
         <v>221100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>238100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>198900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>146900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>189200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>183200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>202700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>190100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>210100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>260600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>298900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>252200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>215000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>249000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>205500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>165200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>122700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>138100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>56200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>140500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>135200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>178500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>192100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>185400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>203000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>205100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>185200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>139000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>266700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>138000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>142000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>116400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>109700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,183 +3871,187 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>751700</v>
+      </c>
+      <c r="E41" s="3">
         <v>685000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>676600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>613600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>692400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>648000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>573200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>477100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>367700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>320000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>648700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>667300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>628600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>618700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1702900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>972200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>983400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>974600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>949100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>853300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>764000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>679500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>738300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>569400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>442400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>361500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>293800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>199600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>102400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>216900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>370500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>321000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>254000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>239300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>279800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>91400</v>
+      </c>
+      <c r="E42" s="3">
         <v>102000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>95000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>490800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>492300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>493500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>104000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>101900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>95600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>85200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>77700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>82300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>81300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>86100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>88300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>101700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>102500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>105600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>101200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>86900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>92300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>87900</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>8</v>
@@ -3975,8 +4065,8 @@
       <c r="AC42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -3999,236 +4089,245 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1164100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1154200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1216100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1145500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1045100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1037500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1045200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1023900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1031400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1067500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1118900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1212000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1140700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1078400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1078100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>981400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>908600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>837500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>864600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>823400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>879500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>872100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>941800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>958400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>930300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>918600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>991300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>936700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>908800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>900200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>851300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>755200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>733300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>703100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>731500</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1140600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1124900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1061900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1029500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1003600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1013100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>986100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>992200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1003400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>977300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>994900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>954200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>941200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>902500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>880100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>827200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>799600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>787900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>777600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>834500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>809900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>794100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>806300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>815700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>831700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>795600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>780600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>763700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>766400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>762500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>736600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>734400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>744500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>723600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>127700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>125700</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
@@ -4242,261 +4341,267 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>58300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>67300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>74600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>77600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>47000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>55400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>78600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>62800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>44700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>51200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>60900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>67900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>44800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>44900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>59200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>58000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>39400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>49000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>56600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>55000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>35500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>43400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>52800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>47300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>30300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>45100</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3302500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3233000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3241400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3483900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3445100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3254400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2773300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2670600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2585400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2508300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2907500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2990400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2869400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2732700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3804800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2961100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2856900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2750300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2743700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2659000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2613600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2478400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2531300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2402700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2262400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2115100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2114700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1956600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1832600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1915100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2001800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1863400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1779100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1696300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1747000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>71300</v>
+      </c>
+      <c r="E47" s="3">
         <v>65200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>69700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>68400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>68500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>64100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>49300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>50600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>56900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>64900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>67100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>61200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>68500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>60000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>57800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>49900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>47000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>42700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>45200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>36300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>57100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>58100</v>
-      </c>
-      <c r="Y47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>8</v>
@@ -4510,8 +4615,8 @@
       <c r="AC47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD47" s="3">
-        <v>0</v>
+      <c r="AD47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
@@ -4534,222 +4639,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4386400</v>
+      </c>
+      <c r="E48" s="3">
         <v>4315900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4242600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4228300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4133900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4143400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4142400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4172900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4185200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4198300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4100000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4036700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3935100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3767300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3591200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3473500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3444000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3427600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3362600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3344400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3373900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3386000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3342700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3345200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3327100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3108600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3065100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3026500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2961400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2924900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2881600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2872500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2887200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2895700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2878700</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1104900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1115300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1123700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1133100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1142500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1153900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1161600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1171100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1180700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1190300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1199800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1209800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1221300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1231900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1131200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1140500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1149800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1159400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1168900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1178400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1247900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1257500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1267200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1276900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1286000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1295500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1262600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1272800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1282800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1293200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1079900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1087300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1095900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1105000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1046900</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>104700</v>
+      </c>
+      <c r="E52" s="3">
         <v>80700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>76400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>68400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>67000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>42600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>51000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>41300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>40800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>70000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>42500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>43500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>44900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>45800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>48600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>51300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>53200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>52200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>53900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>55100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>55800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>49900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>49600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>53100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>50500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>57600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>59700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>63000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>64300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>63900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>80000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>81200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>80000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8969800</v>
+      </c>
+      <c r="E54" s="3">
         <v>8833200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8753800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8982100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8857000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8681100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8177600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8106500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8049000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8003800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8344400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8340600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8137800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7836800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8630800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7673600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7549000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7433200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7372600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7272000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7347600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7235800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7191100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7074400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6928600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6569700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6500000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6315600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6139800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6197500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6027200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5903200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5843400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5777000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5747200</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,147 +5491,151 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>480900</v>
+      </c>
+      <c r="E57" s="3">
         <v>430300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>459900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>474500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>449600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>402400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>405900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>365800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>410500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>410400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>485300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>528200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>546700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>452400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>499100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>405300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>402500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>387000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>352100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>315200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>389000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>351900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>385500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>382800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>405100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>382200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>438900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>431700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>427300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>402900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>379500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>349200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>367300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>323800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>86300</v>
+      </c>
+      <c r="E58" s="3">
         <v>82600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>83800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>482300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>481000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>480200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>478600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>76900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>74600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1900</v>
-      </c>
-      <c r="M58" s="3">
-        <v>1800</v>
       </c>
       <c r="N58" s="3">
         <v>1800</v>
@@ -5510,19 +5644,19 @@
         <v>1800</v>
       </c>
       <c r="P58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>699800</v>
-      </c>
-      <c r="R58" s="3">
-        <v>1700</v>
       </c>
       <c r="S58" s="3">
         <v>1700</v>
       </c>
       <c r="T58" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="U58" s="3">
         <v>1600</v>
@@ -5534,7 +5668,7 @@
         <v>1600</v>
       </c>
       <c r="X58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="Y58" s="3">
         <v>1500</v>
@@ -5546,7 +5680,7 @@
         <v>1500</v>
       </c>
       <c r="AB58" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="AC58" s="3">
         <v>1400</v>
@@ -5558,10 +5692,10 @@
         <v>1400</v>
       </c>
       <c r="AF58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AG58" s="3">
         <v>151300</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>157800</v>
       </c>
       <c r="AH58" s="3">
         <v>157800</v>
@@ -5570,265 +5704,274 @@
         <v>157800</v>
       </c>
       <c r="AJ58" s="3">
+        <v>157800</v>
+      </c>
+      <c r="AK58" s="3">
         <v>27100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>204700</v>
+      </c>
+      <c r="E59" s="3">
         <v>212500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>258700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>241100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>256100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>115900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>123800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>123400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>133600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>463200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>476300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>442900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>419400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>430700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>445500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>409800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>401600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>394000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>421700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>366800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>354000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>370400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>383700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>345300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>334100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>310000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>326200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>282700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>244900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>278500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>287000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>253200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>250900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>274500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1007700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1001600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1100500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1431500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1400300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1265700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1278900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>797700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>828900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>875500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>963400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>972900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>967900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>884800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1644400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>816800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>805800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>782600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>775400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>683600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>744600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>723800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>770700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>729600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>740700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>693600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>766500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>715800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>673600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>832700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>824300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>760200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>776000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>625400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2716200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2688900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2670300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2678000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2681700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2693000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2298000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2706400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2709500</v>
-      </c>
-      <c r="L61" s="3">
-        <v>2484400</v>
       </c>
       <c r="M61" s="3">
         <v>2484400</v>
       </c>
       <c r="N61" s="3">
+        <v>2484400</v>
+      </c>
+      <c r="O61" s="3">
         <v>2484300</v>
-      </c>
-      <c r="O61" s="3">
-        <v>2484200</v>
       </c>
       <c r="P61" s="3">
         <v>2484200</v>
@@ -5837,174 +5980,180 @@
         <v>2484200</v>
       </c>
       <c r="R61" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="S61" s="3">
         <v>2493300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2494000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2493800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2493500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2493200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2493000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2492800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2502700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2502200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2501800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2501300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2500800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2500400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2499800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2499400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2475600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2477000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2478400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2640300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2646500</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>175900</v>
+      </c>
+      <c r="E62" s="3">
         <v>121300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>178900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>193900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>177500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>91800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>176700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>215200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>206700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>976800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>925400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>918900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>906400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>860600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>893900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>919200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>918000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>910500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>898300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>962100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>960100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>948200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>883000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>921400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>891500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>702400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>702500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>711400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>692600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>682800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>733100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>759400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>764300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>751500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>733200</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4470600</v>
+      </c>
+      <c r="E66" s="3">
         <v>4429200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4490200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4855500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4826000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4683800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4290400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4257900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4291300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4336700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4373200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4376100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4358500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4229600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5022500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4229300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4217800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4186900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4167200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4138900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4197700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4164800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4156400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4153200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4134000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3897300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3969800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3927600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3866000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4014900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4033000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3996600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4018700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4017200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4017600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3852800</v>
+      </c>
+      <c r="E72" s="3">
         <v>3776700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3669100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3544400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3459600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3447200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3370500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3339000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3259300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3186800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3443500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3437000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3261900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3102100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3162800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3008500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2906300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2835500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2806700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2742900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2771100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2704800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2643700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2539200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2427800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2315800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2185500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2054000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1949600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1867400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1658200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1578800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1504500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1447100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1396900</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4499200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4404000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4263600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4126600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4031000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3997300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3887200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3848600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3757700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3667100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3971200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3964500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3779300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3607200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3608300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3444300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3331200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3246300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3205400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3133100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3149900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3071000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3034700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2921200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2794600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2672400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2530200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2388000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2273800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2182600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1994200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1906600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1824700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1759800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1729600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>203800</v>
+      </c>
+      <c r="E81" s="3">
         <v>221100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>238100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>198900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>146900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>189200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>183200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>202700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>190100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>210100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>260600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>298900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>252200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>215000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>249000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>205500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>165200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>122700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>138100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>56200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>140500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>135200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>178500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>192100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>185400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>203000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>205100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>185200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>139000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>266700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>138000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>142000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>116400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>109700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>117400</v>
+      </c>
+      <c r="E83" s="3">
         <v>114900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>117300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>115300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>113600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>102800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>102700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>104100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>98400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>118800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>114000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>114300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>109700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>106400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>105600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>104700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>100800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>100900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>100500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>108200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>100300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>98900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>97900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>95900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>94800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>97300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>101400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>104100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>108100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>107700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>97500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>93700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>92500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>93700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>339100</v>
+      </c>
+      <c r="E89" s="3">
         <v>325400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>327100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>278300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>260400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>335300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>339500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>359900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>280400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>420100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>430600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>319000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>325300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>390700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>283600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>228200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>191600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>271100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>298200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>226800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>236700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>329200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>339800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>302400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>236000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>345600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>301000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>331000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>202500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>272800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>197700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>221500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>164100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>213400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>217300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-148100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-201300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-146700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-245000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-76700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-141100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-89800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-126400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-112400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-247500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-182800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-184500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-215600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-238900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-149900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-60700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-174400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-139000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-144200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-203300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>249300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-242800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-81000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-544000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-88900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-126800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-115400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-251800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-183800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-176900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-221200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-429400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-144800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-132700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-87500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-170200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-127100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-51800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-77000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-278300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-95500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-92700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-80100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-202900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-131800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-166300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-381500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-86700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-83100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-57800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-186900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-455000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9065,37 +9299,37 @@
         <v>112300</v>
       </c>
       <c r="F96" s="3">
+        <v>112300</v>
+      </c>
+      <c r="G96" s="3">
         <v>112200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>112000</v>
       </c>
       <c r="H96" s="3">
         <v>112000</v>
       </c>
       <c r="I96" s="3">
-        <v>112400</v>
+        <v>112000</v>
       </c>
       <c r="J96" s="3">
         <v>112400</v>
       </c>
       <c r="K96" s="3">
+        <v>112400</v>
+      </c>
+      <c r="L96" s="3">
         <v>112100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-115900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-117200</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-93600</v>
       </c>
       <c r="O96" s="3">
         <v>-93600</v>
       </c>
       <c r="P96" s="3">
-        <v>-95000</v>
+        <v>-93600</v>
       </c>
       <c r="Q96" s="3">
         <v>-95000</v>
@@ -9104,43 +9338,43 @@
         <v>-95000</v>
       </c>
       <c r="S96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-94800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-75000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-74900</v>
       </c>
       <c r="V96" s="3">
         <v>-74900</v>
       </c>
       <c r="W96" s="3">
-        <v>-74800</v>
+        <v>-74900</v>
       </c>
       <c r="X96" s="3">
         <v>-74800</v>
       </c>
       <c r="Y96" s="3">
-        <v>-74600</v>
+        <v>-74800</v>
       </c>
       <c r="Z96" s="3">
         <v>-74600</v>
       </c>
       <c r="AA96" s="3">
-        <v>-74700</v>
+        <v>-74600</v>
       </c>
       <c r="AB96" s="3">
         <v>-74700</v>
       </c>
       <c r="AC96" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-74500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-59500</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-59400</v>
       </c>
       <c r="AF96" s="3">
         <v>-59400</v>
@@ -9158,10 +9392,13 @@
         <v>-59400</v>
       </c>
       <c r="AK96" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,82 +9724,85 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-113700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-513400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-114300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-135000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>283500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-154500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-123700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-117300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-497000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-265400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-103400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-94200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1045500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>591900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-106700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-95300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-75400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-75300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-85700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-75200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-109700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-75400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-82700</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>-75000</v>
       </c>
       <c r="AB100" s="3">
         <v>-75000</v>
@@ -9565,31 +9811,34 @@
         <v>-75000</v>
       </c>
       <c r="AD100" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-67500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-209800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-44900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-91600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E102" s="3">
         <v>8400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>63000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-78800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>44400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>74800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>96100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>109400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>47700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-328700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>38700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1084200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>730700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>25500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>95800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>89300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>84500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-58800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>168900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>127000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>80900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>67700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>94200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>97200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-114500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-153600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>49500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>67000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>14700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-40500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>66200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>PKG</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2171300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2141000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2146100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2182400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2075300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1979500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1937900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1936000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1952100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1976300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1978400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2125900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2237300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2136400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2043200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2000100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1879900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1807200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1714200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1693700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1541600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1708700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1720000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1750700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1759900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1733700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1746500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1809900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1767500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1690600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1684300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1640100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1584000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1536500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1476600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1484000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1687300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1682300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1675400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1677200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1637600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1607100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1524800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1520300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1504400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1538900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1528100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1607500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1648500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1603200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1533300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1489400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1431100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1403500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1380900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1348300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1209700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1342900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1336700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1339300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1332000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1312300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1321100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1366700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1346900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1334500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1312600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1242800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1219400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1198000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1149500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1154500</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>484000</v>
+      </c>
+      <c r="E10" s="3">
         <v>458700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>470700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>505200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>437700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>372400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>413100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>415700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>447700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>437400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>450300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>518400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>588800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>533200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>509900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>510700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>448800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>403700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>333300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>345400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>331900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>365800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>383300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>411400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>427900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>421400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>425400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>443200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>420600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>356100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>371700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>397300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>364600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>338500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>327100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>329500</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,151 +1417,157 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>14500</v>
+        <v>-12200</v>
       </c>
       <c r="E14" s="3">
         <v>14500</v>
       </c>
       <c r="F14" s="3">
+        <v>14500</v>
+      </c>
+      <c r="G14" s="3">
         <v>11700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>17600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>17000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>58000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-3100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>74600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>7200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>21500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>3500</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>6000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>140100</v>
+      </c>
+      <c r="E15" s="3">
         <v>134900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>133000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>132500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>128500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>126900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>124500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>126800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>124900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>123200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1849800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1846200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1828300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1842400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1790700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1764800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1664600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1667300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1655900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1690600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1690400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1765600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1821500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1779900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1745900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1647800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1585300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1568900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1525000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1484200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1425500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1499600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1484900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1487900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1479500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1458300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1459800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1511400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1497900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1477700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1432300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1397800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1350200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1333400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1283700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1277600</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>321500</v>
+      </c>
+      <c r="E18" s="3">
         <v>294800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>317800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>340000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>284600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>214700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>273300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>268700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>296200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>285700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>288000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>360300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>415800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>356500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>297300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>352300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>294600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>238300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>189200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>209500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>116100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>209100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>235100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>262800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>280400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>275400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>286700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>298500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>269600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>212900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>252000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>242300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>233800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>203100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>192900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>206400</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1949,8 +1983,8 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>3600</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>3600</v>
@@ -1962,19 +1996,19 @@
         <v>3600</v>
       </c>
       <c r="Q20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="R20" s="3">
         <v>4900</v>
-      </c>
-      <c r="R20" s="3">
-        <v>5000</v>
       </c>
       <c r="S20" s="3">
         <v>5000</v>
       </c>
       <c r="T20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="U20" s="3">
         <v>4800</v>
-      </c>
-      <c r="U20" s="3">
-        <v>600</v>
       </c>
       <c r="V20" s="3">
         <v>600</v>
@@ -1986,19 +2020,19 @@
         <v>600</v>
       </c>
       <c r="Y20" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3200</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-3300</v>
       </c>
       <c r="AB20" s="3">
         <v>-3300</v>
       </c>
       <c r="AC20" s="3">
-        <v>-1300</v>
+        <v>-3300</v>
       </c>
       <c r="AD20" s="3">
         <v>-1300</v>
@@ -2007,11 +2041,11 @@
         <v>-1300</v>
       </c>
       <c r="AF20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-700</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
@@ -2025,450 +2059,465 @@
         <v>0</v>
       </c>
       <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3">
         <v>-23400</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>461600</v>
+      </c>
+      <c r="E21" s="3">
         <v>429700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>450800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>472500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>413100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>341600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>397800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>395500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>421100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>408900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>410400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>477900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>533700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>469800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>408600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>462900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>404300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>343900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>290700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>310600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>224900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>310000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>330900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>357500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>373000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>366900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>382700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>398600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>372400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>320300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>359700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>339800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>327500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>295600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>286600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E22" s="3">
         <v>12900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>18800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>19800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>23400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>24900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23500</v>
-      </c>
-      <c r="U22" s="3">
-        <v>24400</v>
       </c>
       <c r="V22" s="3">
         <v>24400</v>
       </c>
       <c r="W22" s="3">
+        <v>24400</v>
+      </c>
+      <c r="X22" s="3">
         <v>25100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>59600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>21100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>22800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>20900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>23100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>25600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>28000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>25400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>25200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>24000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>24300</v>
       </c>
-      <c r="AL22" s="3" t="s">
+      <c r="AM22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>320600</v>
+      </c>
+      <c r="E23" s="3">
         <v>267400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>291600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>318600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>266700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>187500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>248500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>244500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>267800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>253300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>276500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>347400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>340300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>280400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>333900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>274700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>219600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>165400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>185700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>91600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>190100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>172400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>239300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>256000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>249300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>264500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>274100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>245300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>186600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>224000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>216900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>208600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>179100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>168600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E24" s="3">
         <v>63600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>70500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>80500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>67800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>40600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>59300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>61300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>65100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>63200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>64900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>84900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>99100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>86100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>63900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>83200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>67400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>53100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>41800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>46600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>34900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>48400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>36200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>59500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>62400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>62500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>61900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>67400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>58700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>46500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>77200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>77800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>65400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>61700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>57900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>63700</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>241500</v>
+      </c>
+      <c r="E26" s="3">
         <v>203800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>221100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>238100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>198900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>146900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>189200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>183200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>202700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>190100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>211600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>262500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>301500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>254200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>216500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>250700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>207300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>166500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>123600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>139100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>56700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>141700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>136200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>179800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>193600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>186800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>202600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>206700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>186600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>140100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>146800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>139100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>143200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>117400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>110700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>239900</v>
+      </c>
+      <c r="E27" s="3">
         <v>202400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>219600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>236400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>197500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>145900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>187800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>181800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>200800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>188500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>210100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>260600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>298900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>252200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>215000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>249000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>205500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>165200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>122700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>138100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>56200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>140500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>135200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>178500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>192100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>185400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>201000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>205100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>185200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>139000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>144600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>138000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>142000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>116400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>109700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2969,8 +3030,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2987,11 +3048,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>2000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2999,11 +3060,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>122100</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3269,8 +3339,8 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>-3600</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>-3600</v>
@@ -3282,19 +3352,19 @@
         <v>-3600</v>
       </c>
       <c r="Q32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="R32" s="3">
         <v>-4900</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-5000</v>
       </c>
       <c r="S32" s="3">
         <v>-5000</v>
       </c>
       <c r="T32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="U32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-600</v>
       </c>
       <c r="V32" s="3">
         <v>-600</v>
@@ -3306,19 +3376,19 @@
         <v>-600</v>
       </c>
       <c r="Y32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Z32" s="3">
         <v>3100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3200</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>3300</v>
       </c>
       <c r="AB32" s="3">
         <v>3300</v>
       </c>
       <c r="AC32" s="3">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="AD32" s="3">
         <v>1300</v>
@@ -3327,11 +3397,11 @@
         <v>1300</v>
       </c>
       <c r="AF32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AG32" s="3">
         <v>700</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
@@ -3345,120 +3415,126 @@
         <v>0</v>
       </c>
       <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>241500</v>
+      </c>
+      <c r="E33" s="3">
         <v>203800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>221100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>238100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>198900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>146900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>189200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>183200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>202700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>190100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>210100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>260600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>298900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>252200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>215000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>249000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>205500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>165200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>122700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>138100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>56200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>140500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>135200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>178500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>192100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>185400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>203000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>205100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>185200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>139000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>266700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>138000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>142000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>116400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>109700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>241500</v>
+      </c>
+      <c r="E35" s="3">
         <v>203800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>221100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>238100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>198900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>146900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>189200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>183200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>202700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>190100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>210100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>260600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>298900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>252200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>215000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>249000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>205500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>165200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>122700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>138100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>56200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>140500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>135200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>178500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>192100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>185400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>203000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>205100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>185200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>139000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>266700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>138000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>142000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>116400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>109700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,189 +3958,193 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>787900</v>
+      </c>
+      <c r="E41" s="3">
         <v>751700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>685000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>676600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>613600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>692400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>648000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>573200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>477100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>367700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>320000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>648700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>667300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>628600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>618700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1702900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>972200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>983400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>974600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>949100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>853300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>764000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>679500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>738300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>569400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>442400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>361500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>293800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>199600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>102400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>216900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>370500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>321000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>254000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>239300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>279800</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E42" s="3">
         <v>91400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>102000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>95000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>490800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>492300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>493500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>104000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>101900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>95600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>85200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>77700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>82300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>81300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>86100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>88300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>101700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>102500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>105600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>101200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>86900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>92300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>87900</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>8</v>
@@ -4068,8 +4158,8 @@
       <c r="AD42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -4092,228 +4182,237 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1205900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1164100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1154200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1216100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1145500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1045100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1037500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1045200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1023900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1031400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1067500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1118900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1212000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1140700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1078400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1078100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>981400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>908600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>837500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>864600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>823400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>879500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>872100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>941800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>958400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>930300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>918600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>991300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>936700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>908800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>900200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>851300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>755200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>733300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>703100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>731500</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1144700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1140600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1124900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1061900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1029500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1003600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1013100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>986100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>992200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1003400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>977300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>994900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>954200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>941200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>902500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>880100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>827200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>799600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>787900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>777600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>834500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>809900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>794100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>806300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>815700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>831700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>795600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>780600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>763700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>766400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>762500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>736600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>734400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>744500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>723600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4323,14 +4422,14 @@
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>127700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>125700</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -4344,267 +4443,273 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>58300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>67300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>74600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>77600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>47000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>55400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>78600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>62800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>44700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>51200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>60900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>67900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>44800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>44900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>59200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>58000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>39400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>49000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>56600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>55000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>35500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>43400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>52800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>47300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>30300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>45100</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3336600</v>
+      </c>
+      <c r="E46" s="3">
         <v>3302500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3233000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3241400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3483900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3445100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3254400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2773300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2670600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2585400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2508300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2907500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2990400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2869400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2732700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3804800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2961100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2856900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2750300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2743700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2659000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2613600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2478400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2531300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2402700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2262400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2115100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2114700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1956600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1832600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1915100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2001800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1863400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1779100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1696300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1747000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>75600</v>
+      </c>
+      <c r="E47" s="3">
         <v>71300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>65200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>69700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>68400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>68500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>64100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>49300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>50600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>56900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>64900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>67100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>61200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>68500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>60000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>57800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>49900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>47000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>42700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>45200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>36300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>57100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>58100</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
@@ -4618,8 +4723,8 @@
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF47" s="3">
         <v>0</v>
@@ -4642,228 +4747,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4430300</v>
+      </c>
+      <c r="E48" s="3">
         <v>4386400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4315900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4242600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4228300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4133900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4143400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4142400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4172900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4185200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4198300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4100000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4036700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3935100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3767300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3591200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3473500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3444000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3427600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3362600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3344400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3373900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3386000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3342700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3345200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3327100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3108600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3065100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3026500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2961400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2924900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2881600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2872500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2887200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2895700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2878700</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1095500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1104900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1115300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1123700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1133100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1142500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1153900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1161600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1171100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1180700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1190300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1199800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1209800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1221300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1231900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1131200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1140500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1149800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1159400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1168900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1178400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1247900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1257500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1267200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1276900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1286000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1295500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1262600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1272800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1282800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1293200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1079900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1087300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1095900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1105000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1046900</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E52" s="3">
         <v>104700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>80700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>76400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>68400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>67000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>42600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>51000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>41300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>40800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>70000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>42500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>43500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>44900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>45800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>48600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>51300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>53200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>52200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>53900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>55100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>55800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>49900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>49600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>53100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>50500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>57600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>59700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>63000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>64300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>63900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>80000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>81200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>80000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9041200</v>
+      </c>
+      <c r="E54" s="3">
         <v>8969800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8833200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8753800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8982100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8857000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8681100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8177600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8106500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8049000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8003800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8344400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8340600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8137800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7836800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8630800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7673600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7549000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7433200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7372600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7272000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7347600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7235800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7191100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7074400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6928600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6569700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6500000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6315600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6139800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6197500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6027200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5903200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5843400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5777000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5747200</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,153 +5622,157 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>490700</v>
+      </c>
+      <c r="E57" s="3">
         <v>480900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>430300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>459900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>474500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>449600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>402400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>405900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>365800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>410500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>410400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>485300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>528200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>546700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>452400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>499100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>405300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>402500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>387000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>352100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>315200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>389000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>351900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>385500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>382800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>405100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>382200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>438900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>431700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>427300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>402900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>379500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>349200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>367300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>323800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E58" s="3">
         <v>86300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>82600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>83800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>482300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>481000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>480200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>478600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>76900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>74600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1900</v>
-      </c>
-      <c r="N58" s="3">
-        <v>1800</v>
       </c>
       <c r="O58" s="3">
         <v>1800</v>
@@ -5647,19 +5781,19 @@
         <v>1800</v>
       </c>
       <c r="Q58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R58" s="3">
         <v>1700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>699800</v>
-      </c>
-      <c r="S58" s="3">
-        <v>1700</v>
       </c>
       <c r="T58" s="3">
         <v>1700</v>
       </c>
       <c r="U58" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="V58" s="3">
         <v>1600</v>
@@ -5671,7 +5805,7 @@
         <v>1600</v>
       </c>
       <c r="Y58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="Z58" s="3">
         <v>1500</v>
@@ -5683,7 +5817,7 @@
         <v>1500</v>
       </c>
       <c r="AC58" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="AD58" s="3">
         <v>1400</v>
@@ -5695,10 +5829,10 @@
         <v>1400</v>
       </c>
       <c r="AG58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AH58" s="3">
         <v>151300</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>157800</v>
       </c>
       <c r="AI58" s="3">
         <v>157800</v>
@@ -5707,274 +5841,283 @@
         <v>157800</v>
       </c>
       <c r="AK58" s="3">
+        <v>157800</v>
+      </c>
+      <c r="AL58" s="3">
         <v>27100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E59" s="3">
         <v>204700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>212500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>258700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>241100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>256100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>115900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>123800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>123400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>133600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>463200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>476300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>442900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>419400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>430700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>445500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>409800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>401600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>394000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>421700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>366800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>354000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>370400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>383700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>345300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>334100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>310000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>326200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>282700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>244900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>278500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>287000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>253200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>250900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>274500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>943000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1007700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1001600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1100500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1431500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1400300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1265700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1278900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>797700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>828900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>875500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>963400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>972900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>967900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>884800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1644400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>816800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>805800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>782600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>775400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>683600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>744600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>723800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>770700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>729600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>740700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>693600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>766500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>715800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>673600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>832700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>824300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>760200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>776000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>625400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2721900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2716200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2688900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2670300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2678000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2681700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2693000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2298000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2706400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2709500</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2484400</v>
       </c>
       <c r="N61" s="3">
         <v>2484400</v>
       </c>
       <c r="O61" s="3">
+        <v>2484400</v>
+      </c>
+      <c r="P61" s="3">
         <v>2484300</v>
-      </c>
-      <c r="P61" s="3">
-        <v>2484200</v>
       </c>
       <c r="Q61" s="3">
         <v>2484200</v>
@@ -5983,177 +6126,183 @@
         <v>2484200</v>
       </c>
       <c r="S61" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="T61" s="3">
         <v>2493300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2494000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2493800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2493500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2493200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2493000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2492800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2502700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2502200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2501800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2501300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2500800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2500400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2499800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2499400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2475600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2477000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2478400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2640300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2646500</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>179300</v>
+      </c>
+      <c r="E62" s="3">
         <v>175900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>121300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>178900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>193900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>177500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>91800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>176700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>215200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>206700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>976800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>925400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>918900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>906400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>860600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>893900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>919200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>918000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>910500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>898300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>962100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>960100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>948200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>883000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>921400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>891500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>702400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>702500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>711400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>692600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>682800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>733100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>759400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>764300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>751500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>733200</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4409100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4470600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4429200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4490200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4855500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4826000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4683800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4290400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4257900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4291300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4336700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4373200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4376100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4358500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4229600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5022500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4229300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4217800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4186900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4167200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4138900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4197700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4164800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4156400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4153200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4134000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3897300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3969800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3927600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3866000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4014900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4033000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3996600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4018700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4017200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4017600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3973500</v>
+      </c>
+      <c r="E72" s="3">
         <v>3852800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3776700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3669100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3544400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3459600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3447200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3370500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3339000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3259300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3186800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3443500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3437000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3261900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3102100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3162800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3008500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2906300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2835500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2806700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2742900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2771100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2704800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2643700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2539200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2427800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2315800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2185500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2054000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1949600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1867400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1658200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1578800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1504500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1447100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1396900</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4632100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4499200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4404000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4263600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4126600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4031000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3997300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3887200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3848600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3757700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3667100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3971200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3964500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3779300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3607200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3608300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3444300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3331200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3246300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3205400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3133100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3149900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3071000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3034700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2921200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2794600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2672400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2530200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2388000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2273800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2182600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1994200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1906600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1824700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1759800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1729600</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>241500</v>
+      </c>
+      <c r="E81" s="3">
         <v>203800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>221100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>238100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>198900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>146900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>189200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>183200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>202700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>190100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>210100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>260600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>298900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>252200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>215000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>249000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>205500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>165200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>122700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>138100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>56200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>140500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>135200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>178500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>192100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>185400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>203000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>205100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>185200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>139000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>266700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>138000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>142000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>116400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>109700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>119100</v>
+      </c>
+      <c r="E83" s="3">
         <v>117400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>114900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>117300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>115300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>113600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>102800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>102700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>104100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>98400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>118800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>114000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>114300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>109700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>106400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>105600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>104700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>100800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>100900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>100500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>108200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>100300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>98900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>97900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>95900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>94800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>97300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>101400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>104100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>108100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>107700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>97500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>93700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>92500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>93700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>299600</v>
+      </c>
+      <c r="E89" s="3">
         <v>339100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>325400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>327100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>278300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>260400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>335300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>339500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>359900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>280400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>420100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>430600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>319000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>325300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>390700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>283600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>228200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>191600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>271100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>298200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>226800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>236700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>329200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>339800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>302400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>236000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>345600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>301000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>331000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>202500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>272800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>197700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>221500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>164100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>213400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>217300</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-169700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-148100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-201300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-146700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-245000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-76700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-141100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-89800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-126400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-112400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-247500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-182800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-184500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-215600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-238900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-149900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-60700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-174400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-139000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-142800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-144200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-203300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>249300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-242800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-81000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-544000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-88900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-126800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-115400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-251800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-183800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-176900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-221200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-429400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-144800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-132700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-87500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-170200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-127100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-51800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-77000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-278300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-95500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-92700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-80100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-202900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-131800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-166300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-381500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-86700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-83100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-57800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-186900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-455000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,13 +9520,14 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>112300</v>
+        <v>112400</v>
       </c>
       <c r="E96" s="3">
         <v>112300</v>
@@ -9302,37 +9536,37 @@
         <v>112300</v>
       </c>
       <c r="G96" s="3">
+        <v>112300</v>
+      </c>
+      <c r="H96" s="3">
         <v>112200</v>
-      </c>
-      <c r="H96" s="3">
-        <v>112000</v>
       </c>
       <c r="I96" s="3">
         <v>112000</v>
       </c>
       <c r="J96" s="3">
-        <v>112400</v>
+        <v>112000</v>
       </c>
       <c r="K96" s="3">
         <v>112400</v>
       </c>
       <c r="L96" s="3">
+        <v>112400</v>
+      </c>
+      <c r="M96" s="3">
         <v>112100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-115900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-117200</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-93600</v>
       </c>
       <c r="P96" s="3">
         <v>-93600</v>
       </c>
       <c r="Q96" s="3">
-        <v>-95000</v>
+        <v>-93600</v>
       </c>
       <c r="R96" s="3">
         <v>-95000</v>
@@ -9341,43 +9575,43 @@
         <v>-95000</v>
       </c>
       <c r="T96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-94800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-75000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-74900</v>
       </c>
       <c r="W96" s="3">
         <v>-74900</v>
       </c>
       <c r="X96" s="3">
-        <v>-74800</v>
+        <v>-74900</v>
       </c>
       <c r="Y96" s="3">
         <v>-74800</v>
       </c>
       <c r="Z96" s="3">
-        <v>-74600</v>
+        <v>-74800</v>
       </c>
       <c r="AA96" s="3">
         <v>-74600</v>
       </c>
       <c r="AB96" s="3">
-        <v>-74700</v>
+        <v>-74600</v>
       </c>
       <c r="AC96" s="3">
         <v>-74700</v>
       </c>
       <c r="AD96" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-74500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-59500</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-59400</v>
       </c>
       <c r="AG96" s="3">
         <v>-59400</v>
@@ -9395,10 +9629,13 @@
         <v>-59400</v>
       </c>
       <c r="AL96" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,85 +9970,88 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-120600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-128200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-113700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-513400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-114300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-135000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>283500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-154500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-123700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-117300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-497000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-265400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-103400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-94200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1045500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>591900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-106700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-95300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-75400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-75300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-85700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-75200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-109700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-75400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-82700</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>-75000</v>
       </c>
       <c r="AC100" s="3">
         <v>-75000</v>
@@ -9814,31 +10060,34 @@
         <v>-75000</v>
       </c>
       <c r="AE100" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-67500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-209800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-44900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-91600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E102" s="3">
         <v>66700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>63000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-78800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>44400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>74800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>96100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>109400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>47700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-328700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>38700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1084200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>730700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>25500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>95800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>89300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>84500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-58800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>168900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>127000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>80900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>67700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>94200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>97200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-114500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-153600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>49500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>67000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>14700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-40500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>66200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
   <si>
     <t>PKG</t>
   </si>
@@ -656,518 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2363600</v>
+      </c>
+      <c r="E8" s="3">
         <v>2313400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2171300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2141000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2146100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2182400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2075300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1979500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1937900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1936000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1952100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1976300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1978400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2125900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2237300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2136400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2043200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2000100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1879900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1807200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1714200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1693700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1541600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1708700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1720000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1750700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1759900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1733700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1746500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1809900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1767500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1690600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1684300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1640100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1584000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1536500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1476600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1484000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1869100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1790000</v>
       </c>
-      <c r="E9" s="3">
-        <v>1692200</v>
-      </c>
       <c r="F9" s="3">
+        <v>1688300</v>
+      </c>
+      <c r="G9" s="3">
         <v>1682300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1675400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1677200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1637500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1607100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1524800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1520300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1504400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1538900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1528100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1607500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1648500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1603200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1533300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1489400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1431100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1403500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1380900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1348300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1209700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1342900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1336700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1339300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1332000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1312300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1321100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1366700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1346900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1334500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1312600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1242800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1219400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1198000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1149500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1154500</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>494500</v>
+      </c>
+      <c r="E10" s="3">
         <v>523400</v>
       </c>
-      <c r="E10" s="3">
-        <v>479100</v>
-      </c>
       <c r="F10" s="3">
+        <v>483000</v>
+      </c>
+      <c r="G10" s="3">
         <v>458700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>470700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>505200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>437800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>372400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>413100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>415700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>447700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>437400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>450300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>518400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>588800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>533200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>509900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>510700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>448800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>403700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>333300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>345400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>331900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>365800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>383300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>411400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>427900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>421400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>425400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>443200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>420600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>356100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>371700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>397300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>364600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>338500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>327100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>329500</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,163 +1456,169 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>152000</v>
+      </c>
+      <c r="E14" s="3">
         <v>38300</v>
       </c>
-      <c r="E14" s="3">
-        <v>-17000</v>
-      </c>
       <c r="F14" s="3">
-        <v>14500</v>
+        <v>-13100</v>
       </c>
       <c r="G14" s="3">
         <v>14500</v>
       </c>
       <c r="H14" s="3">
+        <v>14500</v>
+      </c>
+      <c r="I14" s="3">
         <v>11700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>17600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>17000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>58000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-3100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>74600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>300</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>3400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>5800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>7200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>21500</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>3500</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>6000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>173800</v>
+      </c>
+      <c r="E15" s="3">
         <v>152600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>140100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>134900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>133000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>132500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>128500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>126900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>124500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>126800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>124900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>123200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1672,8 +1694,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2043200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1950600</v>
       </c>
-      <c r="E17" s="3">
-        <v>1854600</v>
-      </c>
       <c r="F17" s="3">
+        <v>1850700</v>
+      </c>
+      <c r="G17" s="3">
         <v>1846200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1828300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1842400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1790700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1764800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1664600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1667300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1655900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1690600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1690400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1765600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1821500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1779900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1745900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1647800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1585300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1568900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1525000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1484200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1425500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1499600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1484900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1487900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1479500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1458300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1459800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1511400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1497900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1477700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1432300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1397800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1350200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1333400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1283700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1277600</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>320400</v>
+      </c>
+      <c r="E18" s="3">
         <v>362800</v>
       </c>
-      <c r="E18" s="3">
-        <v>316700</v>
-      </c>
       <c r="F18" s="3">
+        <v>320600</v>
+      </c>
+      <c r="G18" s="3">
         <v>294800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>317800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>340000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>284600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>214700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>273300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>268700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>296200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>285700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>288000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>360300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>415800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>356500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>297300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>352300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>294600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>238300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>189200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>209500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>116100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>209100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>235100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>262800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>280400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>275400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>286700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>298500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>269600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>212900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>252000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>242300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>233800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>203100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>192900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>206400</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,8 +2017,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2023,8 +2056,8 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>3600</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>3600</v>
@@ -2036,19 +2069,19 @@
         <v>3600</v>
       </c>
       <c r="S20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T20" s="3">
         <v>4900</v>
-      </c>
-      <c r="T20" s="3">
-        <v>5000</v>
       </c>
       <c r="U20" s="3">
         <v>5000</v>
       </c>
       <c r="V20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="W20" s="3">
         <v>4800</v>
-      </c>
-      <c r="W20" s="3">
-        <v>600</v>
       </c>
       <c r="X20" s="3">
         <v>600</v>
@@ -2060,19 +2093,19 @@
         <v>600</v>
       </c>
       <c r="AA20" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3200</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-3300</v>
       </c>
       <c r="AD20" s="3">
         <v>-3300</v>
       </c>
       <c r="AE20" s="3">
-        <v>-1300</v>
+        <v>-3300</v>
       </c>
       <c r="AF20" s="3">
         <v>-1300</v>
@@ -2081,11 +2114,11 @@
         <v>-1300</v>
       </c>
       <c r="AH20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-700</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
@@ -2099,474 +2132,489 @@
         <v>0</v>
       </c>
       <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3">
         <v>-23400</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>494200</v>
+      </c>
+      <c r="E21" s="3">
         <v>515400</v>
       </c>
-      <c r="E21" s="3">
-        <v>456800</v>
-      </c>
       <c r="F21" s="3">
+        <v>460700</v>
+      </c>
+      <c r="G21" s="3">
         <v>429700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>450800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>472500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>413100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>341600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>397800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>395500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>421100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>408900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>410400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>477900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>533700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>469800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>408600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>462900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>404300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>343900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>290700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>310600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>224900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>310000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>330900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>357500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>373000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>366900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>382700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>398600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>372400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>320300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>359700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>339800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>327500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>295600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>286600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E22" s="3">
         <v>19300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>15100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>24900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23500</v>
-      </c>
-      <c r="W22" s="3">
-        <v>24400</v>
       </c>
       <c r="X22" s="3">
         <v>24400</v>
       </c>
       <c r="Y22" s="3">
+        <v>24400</v>
+      </c>
+      <c r="Z22" s="3">
         <v>25100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>19600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>59600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>21100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>22800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>20900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>23100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>25600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>28000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>25400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>25200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>24000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>24300</v>
       </c>
-      <c r="AN22" s="3" t="s">
+      <c r="AO22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>134500</v>
+      </c>
+      <c r="E23" s="3">
         <v>305200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>320700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>267400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>291600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>318600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>266700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>187500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>248500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>244500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>267800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>253300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>276500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>347400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>400600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>340300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>280400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>333900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>274700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>219600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>165400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>185700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>91600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>190100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>172400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>239300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>256000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>249300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>264500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>274100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>245300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>186600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>224000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>216900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>208600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>179100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>168600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E24" s="3">
         <v>78300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>79100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>63600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>70500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>80500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>67700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>40600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>59300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>61300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>65100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>63200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>64900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>84900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>99100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>86100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>63900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>83200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>67400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>53100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>41800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>46600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>34900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>48400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>36200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>59500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>62400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>62500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>61900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>67400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>58700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>46500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>77200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>77800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>65400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>61700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>57900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>63700</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E26" s="3">
         <v>226900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>241600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>203800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>221100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>238100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>199000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>146900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>189200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>183200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>202700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>190100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>211600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>262500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>301500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>254200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>216500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>250700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>207300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>166500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>123600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>139100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>56700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>141700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>136200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>179800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>193600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>186800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>202600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>206700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>186600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>140100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>146800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>139100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>143200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>117400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>110700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E27" s="3">
         <v>228400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>246000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>202400</v>
       </c>
-      <c r="G27" s="3">
-        <v>219600</v>
-      </c>
       <c r="H27" s="3">
+        <v>211400</v>
+      </c>
+      <c r="I27" s="3">
         <v>239800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>202400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>145900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>187800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>181800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>200800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>188500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>210100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>260600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>298900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>252200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>215000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>249000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>205500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>165200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>122700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>138100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>56200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>140500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>135200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>178500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>192100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>185400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>201000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>205100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>185200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>139000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>144600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>138000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>142000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>116400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>109700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3097,8 +3157,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -3115,11 +3175,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>2000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3127,11 +3187,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>122100</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3443,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3415,8 +3484,8 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>-3600</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>-3600</v>
@@ -3428,19 +3497,19 @@
         <v>-3600</v>
       </c>
       <c r="S32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="T32" s="3">
         <v>-4900</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-5000</v>
       </c>
       <c r="U32" s="3">
         <v>-5000</v>
       </c>
       <c r="V32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="W32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-600</v>
       </c>
       <c r="X32" s="3">
         <v>-600</v>
@@ -3452,19 +3521,19 @@
         <v>-600</v>
       </c>
       <c r="AA32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB32" s="3">
         <v>3100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3200</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>3300</v>
       </c>
       <c r="AD32" s="3">
         <v>3300</v>
       </c>
       <c r="AE32" s="3">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="AF32" s="3">
         <v>1300</v>
@@ -3473,11 +3542,11 @@
         <v>1300</v>
       </c>
       <c r="AH32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AI32" s="3">
         <v>700</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
@@ -3491,126 +3560,132 @@
         <v>0</v>
       </c>
       <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E33" s="3">
         <v>226900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>241600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>203800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>221100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>238100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>199000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>146900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>189200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>183200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>202700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>190100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>210100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>260600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>298900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>252200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>215000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>249000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>205500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>165200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>122700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>138100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>56200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>140500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>135200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>178500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>192100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>185400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>203000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>205100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>185200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>139000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>266700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>138000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>142000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>116400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>109700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E35" s="3">
         <v>226900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>241600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>203800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>221100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>238100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>199000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>146900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>189200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>183200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>202700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>190100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>210100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>260600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>298900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>252200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>215000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>249000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>205500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>165200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>122700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>138100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>56200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>140500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>135200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>178500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>192100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>185400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>203000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>205100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>185200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>139000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>266700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>138000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>142000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>116400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>109700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,201 +4131,205 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>529000</v>
+      </c>
+      <c r="E41" s="3">
         <v>634000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>787900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>751700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>685000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>676600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>613600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>692400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>648000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>573200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>477100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>367700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>320000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>648700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>667300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>628600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>618700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1702900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>972200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>983400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>974600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>949100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>853300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>764000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>679500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>738300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>569400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>442400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>361500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>293800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>199600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>102400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>216900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>370500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>321000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>254000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>239300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>279800</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E42" s="3">
         <v>94700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>92400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>91400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>102000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>95000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>490800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>492300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>493500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>104000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>101900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>95600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>85200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>77700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>82300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>81300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>86100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>88300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>101700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>102500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>105600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>101200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>86900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>92300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>87900</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC42" s="3" t="s">
         <v>8</v>
@@ -4254,8 +4343,8 @@
       <c r="AF42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG42" s="3">
-        <v>0</v>
+      <c r="AG42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH42" s="3">
         <v>0</v>
@@ -4278,240 +4367,249 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1283900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1410500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1205900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1164100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1154200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1216100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1145500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1045100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1037500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1045200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1023900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1031400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1067500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1118900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1212000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1140700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1078400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1078100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>981400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>908600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>837500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>864600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>823400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>879500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>872100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>941800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>958400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>930300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>918600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>991300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>936700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>908800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>900200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>851300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>755200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>733300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>703100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>731500</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1243200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1277100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1144700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1140600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1124900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1061900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1029500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1003600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1013100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>986100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>992200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1003400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>977300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>994900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>954200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>941200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>902500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>880100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>827200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>799600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>787900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>777600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>834500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>809900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>794100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>806300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>815700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>831700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>795600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>780600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>763700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>766400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>762500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>736600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>734400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>744500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>723600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4527,14 +4625,14 @@
       <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>127700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>125700</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
@@ -4548,279 +4646,285 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>58300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>67300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>74600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>77600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>47000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>55400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>78600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>62800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>44700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>51200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>60900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>67900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>44800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>44900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>59200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>58000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>39400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>49000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>56600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>55000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>35500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>43400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>52800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>47300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>30300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>45100</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3213700</v>
+      </c>
+      <c r="E46" s="3">
         <v>3497400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3336600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3302500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3233000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3241400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3483900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3445100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3254400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2773300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2670600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2585400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2508300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2907500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2990400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2869400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2732700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3804800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2961100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2856900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2750300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2743700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2659000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2613600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2478400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2531300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2402700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2262400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2115100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2114700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1956600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1832600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1915100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2001800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1863400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1779100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1696300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1747000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E47" s="3">
         <v>77700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>75600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>71300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>65200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>69700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>68400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>68500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>64100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>49300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>50600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>56900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>64900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>67100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>61200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>68500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>60000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>57800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>49900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>47000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>42700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>45200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>36300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>57100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>58100</v>
-      </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
@@ -4834,8 +4938,8 @@
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG47" s="3">
-        <v>0</v>
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH47" s="3">
         <v>0</v>
@@ -4858,240 +4962,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5361100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5412300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4430300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4386400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4315900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4242600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4228300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4133900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4143400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4142400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4172900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4185200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4198300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4100000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4036700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3935100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3767300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3591200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3473500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3444000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3427600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3362600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3344400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3373900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3386000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3342700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3345200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3327100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3108600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3065100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3026500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2961400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2924900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2881600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2872500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2887200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2895700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2878700</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1975200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1890400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1095500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1104900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1115300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1123700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1133100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1142500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1153900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1161600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1171100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1180700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1190300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1199800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1209800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1221300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1231900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1131200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1140500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1149800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1159400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1168900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1178400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1247900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1257500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1267200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1276900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1286000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1295500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1262600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1272800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1282800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1293200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1079900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1087300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1095900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1105000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1046900</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5438,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E52" s="3">
         <v>102200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>103200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>104700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>80700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>76400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>68400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>67000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>42600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>51000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>41300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>40800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>42000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>70000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>42500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>43500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>44900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>45800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>48600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>51300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>53200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>52200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>53900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>55100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>55800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>49900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>49600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>53100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>50500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>57600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>59700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>63000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>64300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>63900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>80000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>81200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>80000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10725500</v>
+      </c>
+      <c r="E54" s="3">
         <v>10980000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9041200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8969800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8833200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8753800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8982100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8857000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8681100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8177600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8106500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8049000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8003800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8344400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8340600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8137800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7836800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8630800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7673600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7549000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7433200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7372600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7272000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7347600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7235800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7191100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7074400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6928600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6569700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6500000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6315600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6139800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6197500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6027200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5903200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5843400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5777000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>5747200</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,165 +5883,169 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>471400</v>
+      </c>
+      <c r="E57" s="3">
         <v>554200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>490700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>480900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>430300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>459900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>474500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>449600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>402400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>405900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>365800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>410500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>410400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>485300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>528200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>546700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>452400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>499100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>405300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>402500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>387000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>352100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>315200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>389000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>351900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>385500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>382800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>405100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>382200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>438900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>431700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>427300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>402900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>379500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>349200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>367300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>323800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E58" s="3">
         <v>98200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>88900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>86300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>82600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>83800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>482300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>481000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>480200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>478600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>76900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>74600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1900</v>
-      </c>
-      <c r="P58" s="3">
-        <v>1800</v>
       </c>
       <c r="Q58" s="3">
         <v>1800</v>
@@ -5921,19 +6054,19 @@
         <v>1800</v>
       </c>
       <c r="S58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T58" s="3">
         <v>1700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>699800</v>
-      </c>
-      <c r="U58" s="3">
-        <v>1700</v>
       </c>
       <c r="V58" s="3">
         <v>1700</v>
       </c>
       <c r="W58" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="X58" s="3">
         <v>1600</v>
@@ -5945,7 +6078,7 @@
         <v>1600</v>
       </c>
       <c r="AA58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="AB58" s="3">
         <v>1500</v>
@@ -5957,7 +6090,7 @@
         <v>1500</v>
       </c>
       <c r="AE58" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="AF58" s="3">
         <v>1400</v>
@@ -5969,10 +6102,10 @@
         <v>1400</v>
       </c>
       <c r="AI58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>151300</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>157800</v>
       </c>
       <c r="AK58" s="3">
         <v>157800</v>
@@ -5981,292 +6114,301 @@
         <v>157800</v>
       </c>
       <c r="AM58" s="3">
+        <v>157800</v>
+      </c>
+      <c r="AN58" s="3">
         <v>27100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>120600</v>
+      </c>
+      <c r="E59" s="3">
         <v>120700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>115800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>204700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>212500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>258700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>241100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>256100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>115900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>123800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>123400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>133600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>463200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>476300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>442900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>419400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>430700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>445500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>409800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>401600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>394000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>421700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>366800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>354000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>370400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>383700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>345300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>334100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>310000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>326200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>282700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>244900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>278500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>287000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>253200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>250900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>274500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1015100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1107500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>943000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1007700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1001600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1100500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1431500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1400300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1265700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1278900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>797700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>828900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>875500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>963400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>972900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>967900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>884800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1644400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>816800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>805800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>782600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>775400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>683600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>744600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>723800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>770700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>729600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>740700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>693600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>766500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>715800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>673600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>832700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>824300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>760200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>776000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>625400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4262800</v>
+      </c>
+      <c r="E61" s="3">
         <v>4258700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2721900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2716200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2688900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2670300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2678000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2681700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2693000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2298000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2706400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2709500</v>
-      </c>
-      <c r="O61" s="3">
-        <v>2484400</v>
       </c>
       <c r="P61" s="3">
         <v>2484400</v>
       </c>
       <c r="Q61" s="3">
+        <v>2484400</v>
+      </c>
+      <c r="R61" s="3">
         <v>2484300</v>
-      </c>
-      <c r="R61" s="3">
-        <v>2484200</v>
       </c>
       <c r="S61" s="3">
         <v>2484200</v>
@@ -6275,183 +6417,189 @@
         <v>2484200</v>
       </c>
       <c r="U61" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="V61" s="3">
         <v>2493300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2494000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2493800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2493500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2493200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2493000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2492800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2502700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2502200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2501800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2501300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2500800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2500400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2499800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2499400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2475600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2477000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2478400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2640300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2646500</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>130600</v>
+      </c>
+      <c r="E62" s="3">
         <v>186500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>179300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>175900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>121300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>178900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>193900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>177500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>91800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>176700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>215200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>206700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>976800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>925400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>918900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>906400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>860600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>893900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>919200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>918000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>910500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>898300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>962100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>960100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>948200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>883000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>921400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>891500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>702400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>702500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>711400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>692600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>682800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>733100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>759400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>764300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>751500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>733200</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6127500</v>
+      </c>
+      <c r="E66" s="3">
         <v>6224500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4409100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4470600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4429200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4490200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4855500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4826000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4683800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4290400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4257900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4291300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4336700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4373200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4376100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4358500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4229600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5022500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4229300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4217800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4186900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4167200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4138900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4197700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4164800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4156400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4153200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4134000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3897300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3969800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3927600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3866000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4014900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4033000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3996600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4018700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4017200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4017600</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3931000</v>
+      </c>
+      <c r="E72" s="3">
         <v>4087300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3973500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3852800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3776700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3669100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3544400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3459600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3447200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3370500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3339000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3259300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3186800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3443500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3437000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3261900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3102100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3162800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3008500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2906300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2835500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2806700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2742900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2771100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2704800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2643700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2539200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2427800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2315800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2185500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2054000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1949600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1867400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1658200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1578800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1504500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1447100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1396900</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4598000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4755500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4632100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4499200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4404000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4263600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4126600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4031000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3997300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3887200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3848600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3757700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3667100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3971200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3964500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3779300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3607200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3608300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3444300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3331200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3246300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3205400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3133100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3149900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3071000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3034700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2921200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2794600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2672400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2530200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2388000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2273800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2182600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1994200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1906600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1824700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1759800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1729600</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E81" s="3">
         <v>226900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>241600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>203800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>221100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>238100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>199000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>146900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>189200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>183200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>202700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>190100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>210100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>260600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>298900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>252200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>215000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>249000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>205500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>165200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>122700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>138100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>56200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>140500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>135200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>178500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>192100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>185400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>203000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>205100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>185200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>139000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>266700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>138000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>142000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>116400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>109700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8592,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E83" s="3">
         <v>123100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>119100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>117400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>114900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>117300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>115300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>113600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>102800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>102700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>104100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>98400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>118800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>114000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>114300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>109700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>106400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>105600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>104700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>100800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>100900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>100500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>108200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>100300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>98900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>97900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>95900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>94800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>97300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>101400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>104100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>108100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>107700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>97500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>93700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>92500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>93700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>446600</v>
+      </c>
+      <c r="E89" s="3">
         <v>472200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>299600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>339100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>325400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>327100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>278300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>260400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>335300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>339500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>359900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>280400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>420100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>430600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>319000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>325300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>390700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>283600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>228200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>191600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>271100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>298200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>226800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>236700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>329200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>339800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>302400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>236000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>345600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>301000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>331000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>202500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>272800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>197700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>221500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>164100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>213400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>217300</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9468,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-319000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-192100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-169700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-148100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-201300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-146700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-245000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-76700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-141100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-89800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-126400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-112400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-247500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-182800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-184500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-215600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-238900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-149900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-60700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-174400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-139000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-285500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2000400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-142800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-144200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-203300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>249300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-242800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-81000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-544000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-88900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-126800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-115400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-251800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-183800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-176900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-221200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-429400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-144800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-132700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-87500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-170200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-127100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-51800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-77000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-278300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-95500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-92700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-80100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-202900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-131800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-166300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-381500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-86700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-83100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-57800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-186900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-455000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,19 +9987,20 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>112400</v>
+        <v>112500</v>
       </c>
       <c r="E96" s="3">
         <v>112400</v>
       </c>
       <c r="F96" s="3">
-        <v>112300</v>
+        <v>112400</v>
       </c>
       <c r="G96" s="3">
         <v>112300</v>
@@ -9776,37 +10009,37 @@
         <v>112300</v>
       </c>
       <c r="I96" s="3">
+        <v>112300</v>
+      </c>
+      <c r="J96" s="3">
         <v>112200</v>
-      </c>
-      <c r="J96" s="3">
-        <v>112000</v>
       </c>
       <c r="K96" s="3">
         <v>112000</v>
       </c>
       <c r="L96" s="3">
-        <v>112400</v>
+        <v>112000</v>
       </c>
       <c r="M96" s="3">
         <v>112400</v>
       </c>
       <c r="N96" s="3">
+        <v>112400</v>
+      </c>
+      <c r="O96" s="3">
         <v>112100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-115900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-117200</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-93600</v>
       </c>
       <c r="R96" s="3">
         <v>-93600</v>
       </c>
       <c r="S96" s="3">
-        <v>-95000</v>
+        <v>-93600</v>
       </c>
       <c r="T96" s="3">
         <v>-95000</v>
@@ -9815,43 +10048,43 @@
         <v>-95000</v>
       </c>
       <c r="V96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-94800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-75000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-74900</v>
       </c>
       <c r="Y96" s="3">
         <v>-74900</v>
       </c>
       <c r="Z96" s="3">
-        <v>-74800</v>
+        <v>-74900</v>
       </c>
       <c r="AA96" s="3">
         <v>-74800</v>
       </c>
       <c r="AB96" s="3">
-        <v>-74600</v>
+        <v>-74800</v>
       </c>
       <c r="AC96" s="3">
         <v>-74600</v>
       </c>
       <c r="AD96" s="3">
-        <v>-74700</v>
+        <v>-74600</v>
       </c>
       <c r="AE96" s="3">
         <v>-74700</v>
       </c>
       <c r="AF96" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-74500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-59500</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-59400</v>
       </c>
       <c r="AI96" s="3">
         <v>-59400</v>
@@ -9869,10 +10102,13 @@
         <v>-59400</v>
       </c>
       <c r="AN96" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,91 +10461,94 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-266100</v>
+      </c>
+      <c r="E100" s="3">
         <v>1374300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-120600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-128200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-113700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-513400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-114300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-135000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>283500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-154500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-123700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-117300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-497000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-265400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-103400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-94200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1045500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>591900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-106700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-95300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-75400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-75300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-85700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-75200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-109700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-75400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-82700</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>-75000</v>
       </c>
       <c r="AE100" s="3">
         <v>-75000</v>
@@ -10312,31 +10557,34 @@
         <v>-75000</v>
       </c>
       <c r="AG100" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-67500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-209800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-44900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-91600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10373,8 +10621,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10451,120 +10699,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-153900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>36200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>66700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>63000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-78800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>44400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>74800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>96100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>109400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>47700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-328700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>38700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1084200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>730700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>8800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>25500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>95800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>89300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>84500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-58800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>168900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>127000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>80900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>67700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>94200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>97200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-114500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-153600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>49500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>67000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>14700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-40500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>66200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>PKG</t>
   </si>
@@ -656,530 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2367800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2363600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2313400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2171300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2141000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2146100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2182400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2075300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1979500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1937900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1936000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1952100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1976300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1978400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2125900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2237300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2136400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2043200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2000100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1879900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1807200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1714200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1693700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1541600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1708700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1720000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1750700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1759900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1733700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1746500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1809900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1767500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1690600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1684300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1640100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1584000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1536500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1476600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1484000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1863900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1869100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1790000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1688300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1682300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1675400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1677200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1637500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1607100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1524800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1520300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1504400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1538900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1528100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1607500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1648500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1603200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1533300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1489400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1431100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1403500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1380900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1348300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1209700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1342900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1336700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1339300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1332000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1312300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1321100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1366700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1346900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1334500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1312600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1242800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1219400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1198000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1149500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1154500</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>503900</v>
+      </c>
+      <c r="E10" s="3">
         <v>494500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>523400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>483000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>458700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>470700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>505200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>437800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>372400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>413100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>415700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>447700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>437400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>450300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>518400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>588800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>533200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>509900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>510700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>448800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>403700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>333300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>345400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>331900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>365800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>383300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>411400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>427900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>421400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>425400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>443200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>420600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>356100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>371700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>397300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>364600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>338500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>327100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>329500</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,169 +1476,175 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E14" s="3">
         <v>152000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>38300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-13100</v>
-      </c>
-      <c r="G14" s="3">
-        <v>14500</v>
       </c>
       <c r="H14" s="3">
         <v>14500</v>
       </c>
       <c r="I14" s="3">
+        <v>14500</v>
+      </c>
+      <c r="J14" s="3">
         <v>11700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>17600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>11900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>17000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>58000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-3100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>74600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>300</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>5800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>7200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>21500</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>3500</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>6000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>174600</v>
+      </c>
+      <c r="E15" s="3">
         <v>173800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>152600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>140100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>134900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>133000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>132500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>128500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>126900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>124500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>126800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>124900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>123200</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1697,8 +1720,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2049400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2043200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1950600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1850700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1846200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1828300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1842400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1790700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1764800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1664600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1667300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1655900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1690600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1690400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1765600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1821500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1779900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1745900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1647800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1585300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1568900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1525000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1484200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1425500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1499600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1484900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1487900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1479500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1458300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1459800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1511400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1497900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1477700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1432300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1397800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1350200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1333400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1283700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1277600</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>318400</v>
+      </c>
+      <c r="E18" s="3">
         <v>320400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>362800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>320600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>294800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>317800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>340000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>284600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>214700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>273300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>268700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>296200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>285700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>288000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>360300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>415800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>356500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>297300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>352300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>294600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>238300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>189200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>209500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>116100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>209100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>235100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>262800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>280400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>275400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>286700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>298500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>269600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>212900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>252000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>242300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>233800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>203100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>192900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>206400</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,8 +2051,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2059,8 +2093,8 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>3600</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>3600</v>
@@ -2072,19 +2106,19 @@
         <v>3600</v>
       </c>
       <c r="T20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="U20" s="3">
         <v>4900</v>
-      </c>
-      <c r="U20" s="3">
-        <v>5000</v>
       </c>
       <c r="V20" s="3">
         <v>5000</v>
       </c>
       <c r="W20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="X20" s="3">
         <v>4800</v>
-      </c>
-      <c r="X20" s="3">
-        <v>600</v>
       </c>
       <c r="Y20" s="3">
         <v>600</v>
@@ -2096,19 +2130,19 @@
         <v>600</v>
       </c>
       <c r="AB20" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3200</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-3300</v>
       </c>
       <c r="AE20" s="3">
         <v>-3300</v>
       </c>
       <c r="AF20" s="3">
-        <v>-1300</v>
+        <v>-3300</v>
       </c>
       <c r="AG20" s="3">
         <v>-1300</v>
@@ -2117,11 +2151,11 @@
         <v>-1300</v>
       </c>
       <c r="AI20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
       <c r="AK20" s="3">
         <v>0</v>
       </c>
@@ -2135,486 +2169,501 @@
         <v>0</v>
       </c>
       <c r="AO20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="3">
         <v>-23400</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>493000</v>
+      </c>
+      <c r="E21" s="3">
         <v>494200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>515400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>460700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>429700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>450800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>472500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>413100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>341600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>397800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>395500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>421100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>408900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>410400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>477900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>533700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>469800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>408600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>462900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>404300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>343900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>290700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>310600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>224900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>310000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>330900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>357500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>373000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>366900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>382700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>398600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>372400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>320300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>359700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>339800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>327500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>295600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>286600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E22" s="3">
         <v>29000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>19300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>15400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>15100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>21800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>24900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23500</v>
-      </c>
-      <c r="X22" s="3">
-        <v>24400</v>
       </c>
       <c r="Y22" s="3">
         <v>24400</v>
       </c>
       <c r="Z22" s="3">
+        <v>24400</v>
+      </c>
+      <c r="AA22" s="3">
         <v>25100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>59600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>20300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>21100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>22800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>20900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>23000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>25600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>28000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>25400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>25200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>24000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>24300</v>
       </c>
-      <c r="AO22" s="3" t="s">
+      <c r="AP22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>219800</v>
+      </c>
+      <c r="E23" s="3">
         <v>134500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>305200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>320700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>267400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>291600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>318600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>266700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>187500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>248500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>244500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>267800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>253300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>276500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>347400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>400600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>340300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>280400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>333900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>274700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>219600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>165400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>185700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>91600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>190100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>172400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>239300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>256000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>249300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>264500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>274100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>245300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>186600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>224000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>216900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>208600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>179100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>168600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E24" s="3">
         <v>32700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>78300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>79100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>63600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>70500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>80500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>67700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>40600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>59300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>61300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>65100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>63200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>64900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>84900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>99100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>86100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>63900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>83200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>67400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>53100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>41800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>46600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>34900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>48400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>36200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>59500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>62400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>62500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>61900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>67400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>58700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>77200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>77800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>65400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>61700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>57900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>63700</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>170900</v>
+      </c>
+      <c r="E26" s="3">
         <v>101800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>226900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>241600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>203800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>221100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>238100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>199000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>146900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>189200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>183200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>202700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>190100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>211600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>262500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>301500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>254200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>216500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>250700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>207300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>166500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>123600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>139100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>56700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>141700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>136200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>179800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>193600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>186800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>202600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>206700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>186600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>140100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>146800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>139100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>143200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>117400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>110700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>169800</v>
+      </c>
+      <c r="E27" s="3">
         <v>92100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>228400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>246000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>202400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>211400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>239800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>202400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>145900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>187800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>181800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>200800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>188500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>210100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>260600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>298900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>252200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>215000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>249000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>205500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>165200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>122700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>138100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>56200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>140500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>135200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>178500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>192100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>185400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>201000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>205100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>185200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>139000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>144600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>138000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>142000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>116400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>109700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3160,8 +3221,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3178,24 +3239,24 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>2000</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>122100</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,8 +3513,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3487,8 +3557,8 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>-3600</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>-3600</v>
@@ -3500,19 +3570,19 @@
         <v>-3600</v>
       </c>
       <c r="T32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="U32" s="3">
         <v>-4900</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-5000</v>
       </c>
       <c r="V32" s="3">
         <v>-5000</v>
       </c>
       <c r="W32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="X32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-600</v>
       </c>
       <c r="Y32" s="3">
         <v>-600</v>
@@ -3524,19 +3594,19 @@
         <v>-600</v>
       </c>
       <c r="AB32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC32" s="3">
         <v>3100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3200</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>3300</v>
       </c>
       <c r="AE32" s="3">
         <v>3300</v>
       </c>
       <c r="AF32" s="3">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="AG32" s="3">
         <v>1300</v>
@@ -3545,11 +3615,11 @@
         <v>1300</v>
       </c>
       <c r="AI32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>700</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
       <c r="AK32" s="3">
         <v>0</v>
       </c>
@@ -3563,129 +3633,135 @@
         <v>0</v>
       </c>
       <c r="AO32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>170900</v>
+      </c>
+      <c r="E33" s="3">
         <v>101800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>226900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>241600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>203800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>221100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>238100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>199000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>146900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>189200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>183200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>202700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>190100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>210100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>260600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>298900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>252200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>215000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>249000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>205500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>165200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>122700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>138100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>56200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>140500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>135200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>178500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>192100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>185400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>203000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>205100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>185200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>139000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>266700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>138000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>142000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>116400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>109700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>170900</v>
+      </c>
+      <c r="E35" s="3">
         <v>101800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>226900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>241600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>203800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>221100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>238100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>199000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>146900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>189200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>183200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>202700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>190100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>210100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>260600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>298900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>252200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>215000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>249000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>205500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>165200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>122700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>138100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>56200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>140500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>135200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>178500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>192100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>185400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>203000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>205100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>185200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>139000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>266700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>138000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>142000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>116400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>109700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,208 +4218,212 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>397100</v>
+      </c>
+      <c r="E41" s="3">
         <v>529000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>634000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>787900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>751700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>685000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>676600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>613600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>692400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>648000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>573200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>477100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>367700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>320000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>648700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>667300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>628600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>618700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1702900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>972200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>983400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>974600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>949100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>853300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>764000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>679500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>738300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>569400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>442400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>361500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>293800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>199600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>102400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>216900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>370500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>321000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>254000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>239300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>279800</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>146600</v>
+      </c>
+      <c r="E42" s="3">
         <v>71800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>94700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>91400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>102000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>95000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>490800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>492300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>493500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>104000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>101900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>95600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>85200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>77700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>82300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>81300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>86100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>88300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>101700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>102500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>105600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>101200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>86900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>92300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>87900</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4346,8 +4436,8 @@
       <c r="AG42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH42" s="3">
-        <v>0</v>
+      <c r="AH42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI42" s="3">
         <v>0</v>
@@ -4370,246 +4460,255 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1351100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1283900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1410500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1205900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1164100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1154200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1216100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1145500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1045100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1037500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1045200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1023900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1031400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1067500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1118900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1212000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1140700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1078400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1078100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>981400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>908600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>837500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>864600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>823400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>879500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>872100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>941800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>958400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>930300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>918600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>991300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>936700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>908800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>900200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>851300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>755200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>733300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>703100</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>731500</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1258400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1243200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1277100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1144700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1140600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1124900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1061900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1029500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1003600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1013100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>986100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>992200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1003400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>977300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>994900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>954200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>941200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>902500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>880100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>827200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>799600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>787900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>777600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>834500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>809900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>794100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>806300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>815700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>831700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>795600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>780600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>763700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>766400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>762500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>736600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>734400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>744500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>723600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4628,15 +4727,15 @@
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>127700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>125700</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4649,286 +4748,292 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>58300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>67300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>74600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>77600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>47000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>55400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>78600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>62800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>44700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>51200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>60900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>67900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>44800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>44900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>59200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>58000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>39400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>49000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>56600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>55000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>35500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>43400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>52800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>47300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>30300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>45100</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3257600</v>
+      </c>
+      <c r="E46" s="3">
         <v>3213700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3497400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3336600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3302500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3233000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3241400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3483900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3445100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3254400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2773300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2670600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2585400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2508300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2907500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2990400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2869400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2732700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3804800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2961100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2856900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2750300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2743700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2659000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2613600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2478400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2531300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2402700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2262400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2115100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2114700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1956600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1832600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1915100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2001800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1863400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1779100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1696300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1747000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E47" s="3">
         <v>67000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>77700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>75600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>71300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>65200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>69700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>68400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>68500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>64100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>49300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>56900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>64900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>67100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>61200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>68500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>60000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>57800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>49900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>47000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>42700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>45200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>36300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>57100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>58100</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4941,8 +5046,8 @@
       <c r="AG47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH47" s="3">
-        <v>0</v>
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI47" s="3">
         <v>0</v>
@@ -4965,246 +5070,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5373100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5361100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5412300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4430300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4386400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4315900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4242600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4228300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4133900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4143400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4142400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4172900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4185200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4198300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4100000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4036700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3935100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3767300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3591200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3473500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3444000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3427600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3362600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3344400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3373900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3386000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3342700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3345200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3327100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3108600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3065100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3026500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2961400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2924900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2881600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2872500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2887200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2895700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2878700</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1965600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1975200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1890400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1095500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1104900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1115300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1123700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1133100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1142500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1153900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1161600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1171100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1180700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1190300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1199800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1209800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1221300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1231900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1131200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1140500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1149800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1159400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1168900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1178400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1247900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1257500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1267200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1276900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1286000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1295500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1262600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1272800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1282800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1293200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1079900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1087300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1095900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1105000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1046900</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>109800</v>
+      </c>
+      <c r="E52" s="3">
         <v>87000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>102200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>103200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>104700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>80700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>76400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>68400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>67000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>51000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>41300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>40800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>70000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>42500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>43500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>44900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>45800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>48600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>51300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>53200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>52200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>53900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>55100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>55800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>49900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>49600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>53100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>50500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>57600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>59700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>63000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>64300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>63900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>80000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>81200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>80000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10777900</v>
+      </c>
+      <c r="E54" s="3">
         <v>10725500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10980000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9041200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8969800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8833200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8753800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8982100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8857000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8681100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8177600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8106500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8049000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8003800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8344400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8340600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8137800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7836800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8630800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7673600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7549000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7433200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7372600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7272000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7347600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7235800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7191100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7074400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6928600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6569700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6500000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6315600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6139800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6197500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6027200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5903200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5843400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>5777000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>5747200</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,171 +6014,175 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>557000</v>
+      </c>
+      <c r="E57" s="3">
         <v>471400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>554200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>490700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>480900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>430300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>459900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>474500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>449600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>402400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>405900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>365800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>410500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>410400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>485300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>528200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>546700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>452400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>499100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>405300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>402500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>387000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>352100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>315200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>389000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>351900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>385500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>382800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>405100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>382200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>438900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>431700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>427300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>402900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>379500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>349200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>367300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>323800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>104400</v>
+      </c>
+      <c r="E58" s="3">
         <v>102100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>98200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>88900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>86300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>82600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>83800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>482300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>481000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>480200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>478600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>76900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>74600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>1800</v>
       </c>
       <c r="R58" s="3">
         <v>1800</v>
@@ -6057,19 +6191,19 @@
         <v>1800</v>
       </c>
       <c r="T58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U58" s="3">
         <v>1700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>699800</v>
-      </c>
-      <c r="V58" s="3">
-        <v>1700</v>
       </c>
       <c r="W58" s="3">
         <v>1700</v>
       </c>
       <c r="X58" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="Y58" s="3">
         <v>1600</v>
@@ -6081,7 +6215,7 @@
         <v>1600</v>
       </c>
       <c r="AB58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="AC58" s="3">
         <v>1500</v>
@@ -6093,7 +6227,7 @@
         <v>1500</v>
       </c>
       <c r="AF58" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="AG58" s="3">
         <v>1400</v>
@@ -6105,10 +6239,10 @@
         <v>1400</v>
       </c>
       <c r="AJ58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AK58" s="3">
         <v>151300</v>
-      </c>
-      <c r="AK58" s="3">
-        <v>157800</v>
       </c>
       <c r="AL58" s="3">
         <v>157800</v>
@@ -6117,301 +6251,310 @@
         <v>157800</v>
       </c>
       <c r="AN58" s="3">
+        <v>157800</v>
+      </c>
+      <c r="AO58" s="3">
         <v>27100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>113100</v>
+      </c>
+      <c r="E59" s="3">
         <v>120600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>120700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>115800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>204700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>212500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>258700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>241100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>256100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>115900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>123800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>123400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>133600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>463200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>476300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>442900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>419400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>430700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>445500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>409800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>401600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>394000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>421700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>366800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>354000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>370400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>383700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>345300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>334100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>310000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>326200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>282700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>244900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>278500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>287000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>253200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>250900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>274500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1060900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1015100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1107500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>943000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1007700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1001600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1100500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1431500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1400300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1265700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1278900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>797700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>828900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>875500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>963400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>972900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>967900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>884800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1644400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>816800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>805800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>782600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>775400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>683600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>744600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>723800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>770700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>729600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>740700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>693600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>766500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>715800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>673600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>832700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>824300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>760200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>776000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>625400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4262500</v>
+      </c>
+      <c r="E61" s="3">
         <v>4262800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4258700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2721900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2716200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2688900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2670300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2678000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2681700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2693000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2298000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2706400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2709500</v>
-      </c>
-      <c r="P61" s="3">
-        <v>2484400</v>
       </c>
       <c r="Q61" s="3">
         <v>2484400</v>
       </c>
       <c r="R61" s="3">
+        <v>2484400</v>
+      </c>
+      <c r="S61" s="3">
         <v>2484300</v>
-      </c>
-      <c r="S61" s="3">
-        <v>2484200</v>
       </c>
       <c r="T61" s="3">
         <v>2484200</v>
@@ -6420,186 +6563,192 @@
         <v>2484200</v>
       </c>
       <c r="V61" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="W61" s="3">
         <v>2493300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2494000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2493800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2493500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2493200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2493000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2492800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2502700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2502200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2501800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2501300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2500800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2500400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2499800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2499400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2475600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2477000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2478400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2640300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2646500</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>189100</v>
+      </c>
+      <c r="E62" s="3">
         <v>130600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>186500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>179300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>175900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>121300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>178900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>193900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>177500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>91800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>176700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>215200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>206700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>976800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>925400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>918900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>906400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>860600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>893900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>919200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>918000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>910500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>898300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>962100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>960100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>948200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>883000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>921400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>891500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>702400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>702500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>711400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>692600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>682800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>733100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>759400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>764300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>751500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>733200</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6190100</v>
+      </c>
+      <c r="E66" s="3">
         <v>6127500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6224500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4409100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4470600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4429200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4490200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4855500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4826000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4683800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4290400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4257900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4291300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4336700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4373200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4376100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4358500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4229600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5022500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4229300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4217800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4186900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4167200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4138900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4197700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4164800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4156400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4153200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4134000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3897300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3969800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3927600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3866000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4014900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4033000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3996600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4018700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4017200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4017600</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3906400</v>
+      </c>
+      <c r="E72" s="3">
         <v>3931000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4087300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3973500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3852800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3776700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3669100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3544400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3459600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3447200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3370500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3339000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3259300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3186800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3443500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3437000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3261900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3102100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3162800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3008500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2906300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2835500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2806700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2742900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2771100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2704800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2643700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2539200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2427800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2315800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2185500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2054000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1949600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1867400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1658200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1578800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1504500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1447100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1396900</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4587800</v>
+      </c>
+      <c r="E76" s="3">
         <v>4598000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4755500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4632100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4499200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4404000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4263600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4126600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4031000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3997300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3887200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3848600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3757700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3667100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3971200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3964500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3779300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3607200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3608300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3444300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3331200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3246300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3205400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3133100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3149900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3071000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3034700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2921200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2794600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2672400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2530200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2388000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2273800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2182600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1994200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1906600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1824700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1759800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1729600</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>170900</v>
+      </c>
+      <c r="E81" s="3">
         <v>101800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>226900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>241600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>203800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>221100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>238100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>199000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>146900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>189200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>183200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>202700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>190100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>210100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>260600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>298900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>252200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>215000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>249000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>205500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>165200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>122700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>138100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>56200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>140500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>135200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>178500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>192100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>185400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>203000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>205100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>185200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>139000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>266700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>138000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>142000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>116400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>109700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>125500</v>
+      </c>
+      <c r="E83" s="3">
         <v>123600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>123100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>119100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>117400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>114900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>117300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>115300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>113600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>102800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>102700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>104100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>98400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>118800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>114000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>114300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>109700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>106400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>105600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>104700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>100800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>100900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>100500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>108200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>100300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>98900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>97900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>95900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>94800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>97300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>101400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>104100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>108100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>107700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>97500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>93700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>92500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>93700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>329300</v>
+      </c>
+      <c r="E89" s="3">
         <v>446600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>472200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>299600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>339100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>325400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>327100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>278300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>260400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>335300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>339500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>359900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>280400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>420100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>430600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>319000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>325300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>390700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>283600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>228200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>191600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>271100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>298200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>226800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>236700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>329200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>339800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>302400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>236000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>345600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>301000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>331000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>202500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>272800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>197700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>221500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>164100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>213400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>217300</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-164700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-319000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-192100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-169700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-148100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-201300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-146700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-245000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-76700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-141100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-89800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-126400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-112400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-247500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-182800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-184500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-215600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-238900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-149900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-60700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-174400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-139000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-260900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-285500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-142800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-144200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-203300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>249300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-242800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-81000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-544000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-88900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-126800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-115400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-251800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-183800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-176900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-221200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-429400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-144800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-132700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-87500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-170200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-127100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-51800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-77000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-278300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-95500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-92700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-80100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-202900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-131800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-166300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-381500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-86700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-83100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-57800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-186900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-455000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,22 +10221,23 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E96" s="3">
         <v>112500</v>
-      </c>
-      <c r="E96" s="3">
-        <v>112400</v>
       </c>
       <c r="F96" s="3">
         <v>112400</v>
       </c>
       <c r="G96" s="3">
-        <v>112300</v>
+        <v>112400</v>
       </c>
       <c r="H96" s="3">
         <v>112300</v>
@@ -10012,37 +10246,37 @@
         <v>112300</v>
       </c>
       <c r="J96" s="3">
+        <v>112300</v>
+      </c>
+      <c r="K96" s="3">
         <v>112200</v>
-      </c>
-      <c r="K96" s="3">
-        <v>112000</v>
       </c>
       <c r="L96" s="3">
         <v>112000</v>
       </c>
       <c r="M96" s="3">
-        <v>112400</v>
+        <v>112000</v>
       </c>
       <c r="N96" s="3">
         <v>112400</v>
       </c>
       <c r="O96" s="3">
+        <v>112400</v>
+      </c>
+      <c r="P96" s="3">
         <v>112100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-115900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-117200</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-93600</v>
       </c>
       <c r="S96" s="3">
         <v>-93600</v>
       </c>
       <c r="T96" s="3">
-        <v>-95000</v>
+        <v>-93600</v>
       </c>
       <c r="U96" s="3">
         <v>-95000</v>
@@ -10051,43 +10285,43 @@
         <v>-95000</v>
       </c>
       <c r="W96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-94800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-75000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-74900</v>
       </c>
       <c r="Z96" s="3">
         <v>-74900</v>
       </c>
       <c r="AA96" s="3">
-        <v>-74800</v>
+        <v>-74900</v>
       </c>
       <c r="AB96" s="3">
         <v>-74800</v>
       </c>
       <c r="AC96" s="3">
-        <v>-74600</v>
+        <v>-74800</v>
       </c>
       <c r="AD96" s="3">
         <v>-74600</v>
       </c>
       <c r="AE96" s="3">
-        <v>-74700</v>
+        <v>-74600</v>
       </c>
       <c r="AF96" s="3">
         <v>-74700</v>
       </c>
       <c r="AG96" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-74500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-59500</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-59400</v>
       </c>
       <c r="AJ96" s="3">
         <v>-59400</v>
@@ -10105,10 +10339,13 @@
         <v>-59400</v>
       </c>
       <c r="AO96" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,94 +10707,97 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-266100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1374300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-120600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-128200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-113700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-513400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-114300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-135000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>283500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-154500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-123700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-117300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-497000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-265400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-103400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-94200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1045500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>591900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-106700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-95300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-75400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-75300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-85700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-75200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-109700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-75400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-82700</v>
-      </c>
-      <c r="AE100" s="3">
-        <v>-75000</v>
       </c>
       <c r="AF100" s="3">
         <v>-75000</v>
@@ -10560,31 +10806,34 @@
         <v>-75000</v>
       </c>
       <c r="AH100" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-67500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-209800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-44900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-91600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10624,8 +10873,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10702,123 +10951,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-131900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-105000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-153900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>36200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>66700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>8400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>63000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-78800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>44400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>74800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>96100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>109400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>47700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-328700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-18600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>38700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1084200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>730700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>25500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>95800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>89300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>84500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-58800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>168900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>127000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>80900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>67700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>94200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>97200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-114500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-153600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>49500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>67000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>14700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-40500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>66200</v>
       </c>
     </row>
